--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -53213,12 +53213,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -53252,16 +53252,13 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O274" t="n">
-        <v>1</v>
-      </c>
-      <c r="P274" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R274" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.03737952171313338</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -53270,12 +53267,12 @@
       </c>
       <c r="U274" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO274" t="inlineStr">
@@ -53295,7 +53292,7 @@
       </c>
       <c r="AS274" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT274" t="n">
@@ -53308,42 +53305,42 @@
       </c>
       <c r="AV274" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA274" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB274" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC274" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -53375,12 +53372,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -53414,32 +53411,29 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O275" t="n">
-        <v>1</v>
-      </c>
-      <c r="P275" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U275" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="W275" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X275" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi infection</t>
+          <t>Paratyfoidfeber</t>
         </is>
       </c>
       <c r="Y275" t="inlineStr">
@@ -53449,12 +53443,12 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB275" t="inlineStr">
@@ -53464,7 +53458,7 @@
       </c>
       <c r="AC275" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD275" t="inlineStr">
@@ -53499,17 +53493,17 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>US_NNDSS_Paratyphi_current</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
         <is>
-          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Paratyphoid-only source category.</t>
         </is>
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -53532,7 +53526,7 @@
       </c>
       <c r="AS275" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT275" t="n">
@@ -53545,42 +53539,42 @@
       </c>
       <c r="AV275" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA275" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB275" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC275" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -53612,12 +53606,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -53642,7 +53636,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -53651,16 +53645,16 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R276" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -53669,7 +53663,7 @@
       </c>
       <c r="U276" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -53679,7 +53673,7 @@
       </c>
       <c r="AO276" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP276" t="inlineStr">
@@ -53689,12 +53683,12 @@
       </c>
       <c r="AQ276" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS276" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT276" t="n">
@@ -53702,47 +53696,47 @@
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV276" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA276" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB276" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC276" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -53774,12 +53768,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -53804,7 +53798,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -53813,32 +53807,32 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U277" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="V277" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="W277" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X277" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Salmonella Paratyphi infection</t>
         </is>
       </c>
       <c r="Y277" t="inlineStr">
@@ -53863,7 +53857,7 @@
       </c>
       <c r="AC277" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD277" t="inlineStr">
@@ -53898,12 +53892,12 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>US_NNDSS_Paratyphi_current</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
         </is>
       </c>
       <c r="AM277" t="inlineStr">
@@ -53916,7 +53910,7 @@
       </c>
       <c r="AO277" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP277" t="inlineStr">
@@ -53926,12 +53920,12 @@
       </c>
       <c r="AQ277" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS277" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT277" t="n">
@@ -53939,47 +53933,47 @@
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV277" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA277" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB277" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC277" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -54011,12 +54005,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -54050,93 +54044,98 @@
         </is>
       </c>
       <c r="N278" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" t="n">
+        <v>0</v>
+      </c>
+      <c r="P278" t="n">
+        <v>0</v>
+      </c>
+      <c r="R278" t="n">
+        <v>0</v>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO278" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP278" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ278" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT278" t="n">
         <v>1</v>
       </c>
-      <c r="O278" t="n">
-        <v>1</v>
-      </c>
-      <c r="P278" t="n">
-        <v>1</v>
-      </c>
-      <c r="R278" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S278" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA278" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO278" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP278" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ278" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS278" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
-        </is>
-      </c>
-      <c r="AT278" t="n">
-        <v>2</v>
-      </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV278" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -54168,12 +54167,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -54207,32 +54206,32 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U279" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V279" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W279" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X279" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y279" t="inlineStr">
@@ -54242,7 +54241,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -54257,7 +54256,7 @@
       </c>
       <c r="AC279" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD279" t="inlineStr">
@@ -54292,17 +54291,17 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -54310,70 +54309,70 @@
       </c>
       <c r="AO279" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP279" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ279" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS279" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT279" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV279" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA279" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB279" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC279" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -54405,12 +54404,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -54435,7 +54434,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -54444,27 +54443,22 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R280" t="n">
-        <v>0</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S280" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
-        <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA280" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -54472,70 +54466,70 @@
       </c>
       <c r="AO280" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP280" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ280" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS280" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT280" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU280" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV280" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA280" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB280" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC280" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -54567,12 +54561,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -54597,7 +54591,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -54606,32 +54600,32 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U281" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="V281" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="W281" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X281" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y281" t="inlineStr">
@@ -54641,7 +54635,7 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
@@ -54656,7 +54650,7 @@
       </c>
       <c r="AC281" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD281" t="inlineStr">
@@ -54691,17 +54685,17 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -54709,70 +54703,70 @@
       </c>
       <c r="AO281" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP281" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ281" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS281" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT281" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV281" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ281" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA281" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB281" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC281" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -54804,12 +54798,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -54859,6 +54853,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA282" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -54866,70 +54865,70 @@
       </c>
       <c r="AO282" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP282" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ282" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS282" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT282" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV282" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ282" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA282" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB282" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC282" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -54961,12 +54960,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -55010,22 +55009,22 @@
       </c>
       <c r="U283" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V283" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W283" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X283" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y283" t="inlineStr">
@@ -55035,7 +55034,7 @@
       </c>
       <c r="Z283" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
@@ -55050,7 +55049,7 @@
       </c>
       <c r="AC283" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD283" t="inlineStr">
@@ -55085,17 +55084,17 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN283" t="b">
@@ -55103,70 +55102,70 @@
       </c>
       <c r="AO283" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP283" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ283" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS283" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT283" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV283" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ283" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA283" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB283" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC283" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55198,12 +55197,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -55228,7 +55227,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -55237,98 +55236,93 @@
         </is>
       </c>
       <c r="N284" t="n">
+        <v>0</v>
+      </c>
+      <c r="O284" t="n">
+        <v>0</v>
+      </c>
+      <c r="P284" t="n">
+        <v>0</v>
+      </c>
+      <c r="R284" t="n">
+        <v>0</v>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO284" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP284" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ284" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS284" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT284" t="n">
         <v>2</v>
       </c>
-      <c r="O284" t="n">
-        <v>2</v>
-      </c>
-      <c r="P284" t="n">
-        <v>2</v>
-      </c>
-      <c r="R284" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S284" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U284" t="inlineStr">
-        <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA284" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO284" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP284" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ284" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS284" t="inlineStr">
-        <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT284" t="n">
-        <v>1</v>
-      </c>
       <c r="AU284" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV284" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW284" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ284" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA284" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB284" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC284" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -55360,12 +55354,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -55390,7 +55384,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -55399,32 +55393,32 @@
         </is>
       </c>
       <c r="N285" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O285" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P285" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U285" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="V285" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="W285" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X285" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi infection</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y285" t="inlineStr">
@@ -55434,7 +55428,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -55449,7 +55443,7 @@
       </c>
       <c r="AC285" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD285" t="inlineStr">
@@ -55484,17 +55478,17 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>US_NNDSS_Paratyphi_current</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
         <is>
-          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -55507,7 +55501,7 @@
       </c>
       <c r="AP285" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ285" t="inlineStr">
@@ -55517,55 +55511,55 @@
       </c>
       <c r="AS285" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT285" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV285" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ285" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA285" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB285" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC285" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -55597,12 +55591,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -55627,7 +55621,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -55636,16 +55630,16 @@
         </is>
       </c>
       <c r="N286" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O286" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P286" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R286" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S286" t="inlineStr">
         <is>
@@ -55654,7 +55648,7 @@
       </c>
       <c r="U286" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AA286" t="inlineStr">
@@ -55664,7 +55658,7 @@
       </c>
       <c r="AO286" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP286" t="inlineStr">
@@ -55674,12 +55668,12 @@
       </c>
       <c r="AQ286" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS286" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT286" t="n">
@@ -55687,47 +55681,47 @@
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV286" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW286" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ286" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA286" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB286" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC286" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -55759,12 +55753,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -55789,7 +55783,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -55798,32 +55792,32 @@
         </is>
       </c>
       <c r="N287" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O287" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P287" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U287" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="V287" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="W287" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X287" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Salmonella Paratyphi infection</t>
         </is>
       </c>
       <c r="Y287" t="inlineStr">
@@ -55848,7 +55842,7 @@
       </c>
       <c r="AC287" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD287" t="inlineStr">
@@ -55883,12 +55877,12 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>US_NNDSS_Paratyphi_current</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
         </is>
       </c>
       <c r="AM287" t="inlineStr">
@@ -55901,7 +55895,7 @@
       </c>
       <c r="AO287" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP287" t="inlineStr">
@@ -55911,12 +55905,12 @@
       </c>
       <c r="AQ287" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS287" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT287" t="n">
@@ -55924,47 +55918,47 @@
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV287" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW287" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ287" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA287" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB287" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC287" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -55996,12 +55990,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -56051,6 +56045,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA288" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -56058,70 +56057,70 @@
       </c>
       <c r="AO288" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP288" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ288" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS288" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT288" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV288" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ288" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA288" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB288" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC288" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56153,12 +56152,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -56202,22 +56201,22 @@
       </c>
       <c r="U289" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V289" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W289" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X289" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y289" t="inlineStr">
@@ -56227,7 +56226,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -56242,7 +56241,7 @@
       </c>
       <c r="AC289" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD289" t="inlineStr">
@@ -56277,17 +56276,17 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN289" t="b">
@@ -56295,70 +56294,70 @@
       </c>
       <c r="AO289" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP289" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ289" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS289" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT289" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU289" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV289" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW289" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ289" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA289" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB289" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC289" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56390,12 +56389,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -56420,7 +56419,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -56445,11 +56444,6 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U290" t="inlineStr">
-        <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA290" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -56457,70 +56451,70 @@
       </c>
       <c r="AO290" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP290" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ290" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS290" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT290" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV290" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW290" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX290" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY290" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ290" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA290" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB290" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC290" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -56552,12 +56546,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -56582,7 +56576,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -56601,22 +56595,22 @@
       </c>
       <c r="U291" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="V291" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="W291" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X291" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y291" t="inlineStr">
@@ -56626,7 +56620,7 @@
       </c>
       <c r="Z291" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA291" t="inlineStr">
@@ -56641,7 +56635,7 @@
       </c>
       <c r="AC291" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD291" t="inlineStr">
@@ -56676,17 +56670,17 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM291" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN291" t="b">
@@ -56694,70 +56688,70 @@
       </c>
       <c r="AO291" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP291" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ291" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS291" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT291" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU291" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV291" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW291" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX291" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY291" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ291" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA291" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB291" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC291" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -56789,12 +56783,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -56844,6 +56838,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA292" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -56851,70 +56850,70 @@
       </c>
       <c r="AO292" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP292" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ292" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS292" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT292" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU292" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV292" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW292" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX292" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY292" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ292" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA292" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB292" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC292" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56946,12 +56945,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -56995,22 +56994,22 @@
       </c>
       <c r="U293" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V293" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W293" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X293" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y293" t="inlineStr">
@@ -57020,7 +57019,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -57035,7 +57034,7 @@
       </c>
       <c r="AC293" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD293" t="inlineStr">
@@ -57070,17 +57069,17 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN293" t="b">
@@ -57088,70 +57087,70 @@
       </c>
       <c r="AO293" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP293" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ293" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS293" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT293" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU293" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV293" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW293" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX293" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY293" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ293" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA293" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB293" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC293" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -57183,12 +57182,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -57213,12 +57212,12 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N294" t="n">
@@ -57227,6 +57226,9 @@
       <c r="O294" t="n">
         <v>0</v>
       </c>
+      <c r="P294" t="n">
+        <v>0</v>
+      </c>
       <c r="R294" t="n">
         <v>0</v>
       </c>
@@ -57235,82 +57237,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
-        <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
-        </is>
-      </c>
       <c r="AA294" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO294" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP294" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ294" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS294" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT294" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU294" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV294" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW294" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX294" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY294" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ294" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA294" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB294" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC294" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -57342,12 +57339,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -57372,12 +57369,12 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N295" t="n">
@@ -57386,19 +57383,22 @@
       <c r="O295" t="n">
         <v>0</v>
       </c>
+      <c r="P295" t="n">
+        <v>0</v>
+      </c>
       <c r="U295" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="V295" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="W295" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X295" t="inlineStr">
@@ -57413,12 +57413,12 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB295" t="inlineStr">
@@ -57428,7 +57428,7 @@
       </c>
       <c r="AC295" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD295" t="inlineStr">
@@ -57463,12 +57463,12 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>AU_NINDSS_current</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
         <is>
-          <t>Australia NINDSS paratyphoid-only notifications; excludes typhoid fever.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM295" t="inlineStr">
@@ -57481,70 +57481,70 @@
       </c>
       <c r="AO295" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP295" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ295" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS295" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT295" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU295" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV295" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW295" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX295" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY295" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ295" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA295" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB295" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC295" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -57576,12 +57576,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -57630,7 +57630,7 @@
       </c>
       <c r="U296" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
@@ -57640,7 +57640,7 @@
       </c>
       <c r="AO296" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP296" t="inlineStr">
@@ -57650,12 +57650,12 @@
       </c>
       <c r="AQ296" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS296" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT296" t="n">
@@ -57663,47 +57663,47 @@
       </c>
       <c r="AU296" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV296" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW296" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX296" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY296" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ296" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA296" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB296" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC296" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -57735,12 +57735,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -57781,22 +57781,22 @@
       </c>
       <c r="U297" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V297" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W297" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_AU_NINDSS</t>
         </is>
       </c>
       <c r="X297" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y297" t="inlineStr">
@@ -57806,7 +57806,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
@@ -57821,7 +57821,7 @@
       </c>
       <c r="AC297" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:AU:national</t>
         </is>
       </c>
       <c r="AD297" t="inlineStr">
@@ -57856,12 +57856,12 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>AU_NINDSS_current</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
+          <t>Australia NINDSS paratyphoid-only notifications; excludes typhoid fever.</t>
         </is>
       </c>
       <c r="AM297" t="inlineStr">
@@ -57874,7 +57874,7 @@
       </c>
       <c r="AO297" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP297" t="inlineStr">
@@ -57884,12 +57884,12 @@
       </c>
       <c r="AQ297" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS297" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT297" t="n">
@@ -57897,47 +57897,47 @@
       </c>
       <c r="AU297" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV297" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW297" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX297" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY297" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ297" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA297" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB297" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC297" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -57969,12 +57969,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -58023,7 +58023,7 @@
       </c>
       <c r="U298" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -58043,12 +58043,12 @@
       </c>
       <c r="AQ298" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS298" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AT298" t="n">
@@ -58056,47 +58056,47 @@
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV298" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW298" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ298" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA298" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB298" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC298" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -58128,12 +58128,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -58174,22 +58174,22 @@
       </c>
       <c r="U299" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="W299" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X299" t="inlineStr">
         <is>
-          <t>파라티푸스</t>
+          <t>Salmonella Paratyphi</t>
         </is>
       </c>
       <c r="Y299" t="inlineStr">
@@ -58199,7 +58199,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -58214,7 +58214,7 @@
       </c>
       <c r="AC299" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD299" t="inlineStr">
@@ -58249,12 +58249,12 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>KR_KDCA_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
         <is>
-          <t>Korea KDCA paratyphoid-only notifications.</t>
+          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
         </is>
       </c>
       <c r="AM299" t="inlineStr">
@@ -58277,12 +58277,12 @@
       </c>
       <c r="AQ299" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS299" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AT299" t="n">
@@ -58290,47 +58290,47 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV299" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW299" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ299" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA299" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB299" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC299" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -58362,12 +58362,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -58416,7 +58416,7 @@
       </c>
       <c r="U300" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -58441,7 +58441,7 @@
       </c>
       <c r="AS300" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT300" t="n">
@@ -58454,42 +58454,42 @@
       </c>
       <c r="AV300" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW300" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX300" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY300" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ300" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA300" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB300" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC300" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -58521,12 +58521,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -58567,22 +58567,22 @@
       </c>
       <c r="U301" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V301" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W301" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_KR_KDCA</t>
         </is>
       </c>
       <c r="X301" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>파라티푸스</t>
         </is>
       </c>
       <c r="Y301" t="inlineStr">
@@ -58592,7 +58592,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -58607,7 +58607,7 @@
       </c>
       <c r="AC301" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:KR:national</t>
         </is>
       </c>
       <c r="AD301" t="inlineStr">
@@ -58642,17 +58642,17 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>KR_KDCA_current</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+          <t>Korea KDCA paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -58675,7 +58675,7 @@
       </c>
       <c r="AS301" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT301" t="n">
@@ -58688,40 +58688,433 @@
       </c>
       <c r="AV301" t="inlineStr">
         <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW301" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX301" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY301" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA301" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB301" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC301" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N302" t="n">
+        <v>0</v>
+      </c>
+      <c r="O302" t="n">
+        <v>0</v>
+      </c>
+      <c r="R302" t="n">
+        <v>0</v>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO302" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP302" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ302" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS302" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT302" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU302" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV302" t="inlineStr">
+        <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW301" t="inlineStr">
+      <c r="AW302" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX301" t="inlineStr">
+      <c r="AX302" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY301" t="inlineStr">
+      <c r="AY302" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ301" t="inlineStr">
+      <c r="AZ302" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA301" t="inlineStr">
+      <c r="BA302" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB301" t="inlineStr">
+      <c r="BB302" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC301" t="inlineStr">
+      <c r="BC302" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N303" t="n">
+        <v>0</v>
+      </c>
+      <c r="O303" t="n">
+        <v>0</v>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W303" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X303" t="inlineStr">
+        <is>
+          <t>Paratyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y303" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z303" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB303" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC303" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD303" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE303" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF303" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG303" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH303" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI303" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ303" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK303" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+        </is>
+      </c>
+      <c r="AM303" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN303" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO303" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP303" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ303" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS303" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT303" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU303" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV303" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW303" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX303" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY303" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA303" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB303" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC303" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -58843,7 +59236,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10">
@@ -58853,7 +59246,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11">
@@ -58873,7 +59266,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -58905,7 +59298,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -52073,13 +52073,13 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R268" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
@@ -52232,10 +52232,10 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U269" t="inlineStr">
         <is>
@@ -57576,12 +57576,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -57606,22 +57606,25 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N296" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O296" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="P296" t="n">
+        <v>3</v>
       </c>
       <c r="R296" t="n">
-        <v>0</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S296" t="inlineStr">
         <is>
@@ -57630,12 +57633,12 @@
       </c>
       <c r="U296" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AA296" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO296" t="inlineStr">
@@ -57655,7 +57658,7 @@
       </c>
       <c r="AS296" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT296" t="n">
@@ -57668,42 +57671,42 @@
       </c>
       <c r="AV296" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW296" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX296" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY296" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ296" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA296" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB296" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC296" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -57735,12 +57738,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -57765,38 +57768,41 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N297" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O297" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="P297" t="n">
+        <v>3</v>
       </c>
       <c r="U297" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V297" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W297" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X297" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y297" t="inlineStr">
@@ -57811,7 +57817,7 @@
       </c>
       <c r="AA297" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB297" t="inlineStr">
@@ -57821,7 +57827,7 @@
       </c>
       <c r="AC297" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD297" t="inlineStr">
@@ -57856,17 +57862,17 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>AU_NINDSS_current</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
         <is>
-          <t>Australia NINDSS paratyphoid-only notifications; excludes typhoid fever.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -57889,7 +57895,7 @@
       </c>
       <c r="AS297" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT297" t="n">
@@ -57902,42 +57908,42 @@
       </c>
       <c r="AV297" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW297" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX297" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY297" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ297" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA297" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB297" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC297" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -57969,12 +57975,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -58023,7 +58029,7 @@
       </c>
       <c r="U298" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA298" t="inlineStr">
@@ -58033,7 +58039,7 @@
       </c>
       <c r="AO298" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP298" t="inlineStr">
@@ -58043,12 +58049,12 @@
       </c>
       <c r="AQ298" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS298" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT298" t="n">
@@ -58056,47 +58062,47 @@
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV298" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW298" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ298" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA298" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB298" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC298" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -58128,12 +58134,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -58174,22 +58180,22 @@
       </c>
       <c r="U299" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W299" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_AU_NINDSS</t>
         </is>
       </c>
       <c r="X299" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y299" t="inlineStr">
@@ -58199,7 +58205,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -58214,7 +58220,7 @@
       </c>
       <c r="AC299" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:AU:national</t>
         </is>
       </c>
       <c r="AD299" t="inlineStr">
@@ -58249,12 +58255,12 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>AU_NINDSS_current</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
+          <t>Australia NINDSS paratyphoid-only notifications; excludes typhoid fever.</t>
         </is>
       </c>
       <c r="AM299" t="inlineStr">
@@ -58267,7 +58273,7 @@
       </c>
       <c r="AO299" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP299" t="inlineStr">
@@ -58277,12 +58283,12 @@
       </c>
       <c r="AQ299" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS299" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT299" t="n">
@@ -58290,47 +58296,47 @@
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV299" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW299" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ299" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA299" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB299" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC299" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -58362,12 +58368,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -58416,7 +58422,7 @@
       </c>
       <c r="U300" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -58436,12 +58442,12 @@
       </c>
       <c r="AQ300" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS300" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AT300" t="n">
@@ -58449,47 +58455,47 @@
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV300" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW300" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX300" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY300" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ300" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA300" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB300" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC300" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -58521,12 +58527,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -58567,22 +58573,22 @@
       </c>
       <c r="U301" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="V301" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="W301" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X301" t="inlineStr">
         <is>
-          <t>파라티푸스</t>
+          <t>Salmonella Paratyphi</t>
         </is>
       </c>
       <c r="Y301" t="inlineStr">
@@ -58592,7 +58598,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -58607,7 +58613,7 @@
       </c>
       <c r="AC301" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD301" t="inlineStr">
@@ -58642,12 +58648,12 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>KR_KDCA_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
         <is>
-          <t>Korea KDCA paratyphoid-only notifications.</t>
+          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
         </is>
       </c>
       <c r="AM301" t="inlineStr">
@@ -58670,12 +58676,12 @@
       </c>
       <c r="AQ301" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS301" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AT301" t="n">
@@ -58683,47 +58689,47 @@
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV301" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW301" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ301" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA301" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB301" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC301" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -58755,12 +58761,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -58809,7 +58815,7 @@
       </c>
       <c r="U302" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -58834,7 +58840,7 @@
       </c>
       <c r="AS302" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT302" t="n">
@@ -58847,42 +58853,42 @@
       </c>
       <c r="AV302" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW302" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ302" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA302" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB302" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC302" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -58914,12 +58920,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -58960,22 +58966,22 @@
       </c>
       <c r="U303" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V303" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W303" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_KR_KDCA</t>
         </is>
       </c>
       <c r="X303" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>파라티푸스</t>
         </is>
       </c>
       <c r="Y303" t="inlineStr">
@@ -58985,7 +58991,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -59000,7 +59006,7 @@
       </c>
       <c r="AC303" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:KR:national</t>
         </is>
       </c>
       <c r="AD303" t="inlineStr">
@@ -59035,17 +59041,17 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>KR_KDCA_current</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+          <t>Korea KDCA paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN303" t="b">
@@ -59068,7 +59074,7 @@
       </c>
       <c r="AS303" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT303" t="n">
@@ -59081,40 +59087,433 @@
       </c>
       <c r="AV303" t="inlineStr">
         <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW303" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX303" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY303" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ303" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA303" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB303" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC303" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N304" t="n">
+        <v>0</v>
+      </c>
+      <c r="O304" t="n">
+        <v>0</v>
+      </c>
+      <c r="R304" t="n">
+        <v>0</v>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO304" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP304" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ304" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS304" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT304" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU304" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV304" t="inlineStr">
+        <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW303" t="inlineStr">
+      <c r="AW304" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX303" t="inlineStr">
+      <c r="AX304" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY303" t="inlineStr">
+      <c r="AY304" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ303" t="inlineStr">
+      <c r="AZ304" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA303" t="inlineStr">
+      <c r="BA304" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB303" t="inlineStr">
+      <c r="BB304" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC303" t="inlineStr">
+      <c r="BC304" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N305" t="n">
+        <v>0</v>
+      </c>
+      <c r="O305" t="n">
+        <v>0</v>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W305" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X305" t="inlineStr">
+        <is>
+          <t>Paratyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y305" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z305" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB305" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC305" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD305" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE305" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF305" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG305" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH305" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI305" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ305" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK305" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+        </is>
+      </c>
+      <c r="AM305" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN305" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO305" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP305" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ305" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS305" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT305" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU305" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV305" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW305" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX305" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY305" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA305" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB305" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC305" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -59236,7 +59635,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10">
@@ -59246,7 +59645,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11">
@@ -59266,7 +59665,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -59298,7 +59697,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -52859,13 +52859,13 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O272" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R272" t="n">
-        <v>0.08844879128977531</v>
+        <v>0.1061385495477304</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -53018,10 +53018,10 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O273" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U273" t="inlineStr">
         <is>
@@ -59697,7 +59697,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -35543,7 +35543,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -43905,7 +43905,7 @@
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -50828,13 +50828,13 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R260" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
@@ -50987,10 +50987,10 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U261" t="inlineStr">
         <is>
@@ -51079,7 +51079,7 @@
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -57975,12 +57975,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -58005,12 +58005,12 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N298" t="n">
@@ -58019,6 +58019,9 @@
       <c r="O298" t="n">
         <v>0</v>
       </c>
+      <c r="P298" t="n">
+        <v>0</v>
+      </c>
       <c r="R298" t="n">
         <v>0</v>
       </c>
@@ -58027,82 +58030,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
-        <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
-        </is>
-      </c>
       <c r="AA298" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO298" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP298" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ298" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS298" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT298" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV298" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW298" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ298" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA298" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB298" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC298" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -58134,12 +58132,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -58164,12 +58162,12 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N299" t="n">
@@ -58178,19 +58176,22 @@
       <c r="O299" t="n">
         <v>0</v>
       </c>
+      <c r="P299" t="n">
+        <v>0</v>
+      </c>
       <c r="U299" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="W299" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X299" t="inlineStr">
@@ -58205,12 +58206,12 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB299" t="inlineStr">
@@ -58220,7 +58221,7 @@
       </c>
       <c r="AC299" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD299" t="inlineStr">
@@ -58255,12 +58256,12 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>AU_NINDSS_current</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
         <is>
-          <t>Australia NINDSS paratyphoid-only notifications; excludes typhoid fever.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM299" t="inlineStr">
@@ -58273,70 +58274,70 @@
       </c>
       <c r="AO299" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP299" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ299" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS299" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT299" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV299" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW299" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ299" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA299" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB299" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC299" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -58368,12 +58369,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -58422,7 +58423,7 @@
       </c>
       <c r="U300" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
@@ -58432,7 +58433,7 @@
       </c>
       <c r="AO300" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP300" t="inlineStr">
@@ -58442,12 +58443,12 @@
       </c>
       <c r="AQ300" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS300" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT300" t="n">
@@ -58455,47 +58456,47 @@
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV300" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW300" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX300" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY300" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ300" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA300" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB300" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC300" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -58527,12 +58528,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -58573,22 +58574,22 @@
       </c>
       <c r="U301" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V301" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W301" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_AU_NINDSS</t>
         </is>
       </c>
       <c r="X301" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y301" t="inlineStr">
@@ -58598,7 +58599,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -58613,7 +58614,7 @@
       </c>
       <c r="AC301" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:AU:national</t>
         </is>
       </c>
       <c r="AD301" t="inlineStr">
@@ -58648,17 +58649,17 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>AU_NINDSS_current</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
+          <t>Australia NINDSS paratyphoid-only notifications; excludes typhoid fever.</t>
         </is>
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -58666,7 +58667,7 @@
       </c>
       <c r="AO301" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP301" t="inlineStr">
@@ -58676,12 +58677,12 @@
       </c>
       <c r="AQ301" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS301" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT301" t="n">
@@ -58689,47 +58690,47 @@
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV301" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW301" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ301" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA301" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB301" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC301" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -58761,12 +58762,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -58815,7 +58816,7 @@
       </c>
       <c r="U302" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AA302" t="inlineStr">
@@ -58835,12 +58836,12 @@
       </c>
       <c r="AQ302" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS302" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AT302" t="n">
@@ -58848,47 +58849,47 @@
       </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV302" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW302" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ302" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA302" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB302" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC302" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -58920,12 +58921,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -58966,22 +58967,22 @@
       </c>
       <c r="U303" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="V303" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="W303" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X303" t="inlineStr">
         <is>
-          <t>파라티푸스</t>
+          <t>Salmonella Paratyphi</t>
         </is>
       </c>
       <c r="Y303" t="inlineStr">
@@ -58991,7 +58992,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -59006,7 +59007,7 @@
       </c>
       <c r="AC303" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD303" t="inlineStr">
@@ -59041,12 +59042,12 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>KR_KDCA_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
         <is>
-          <t>Korea KDCA paratyphoid-only notifications.</t>
+          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
         </is>
       </c>
       <c r="AM303" t="inlineStr">
@@ -59069,12 +59070,12 @@
       </c>
       <c r="AQ303" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS303" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AT303" t="n">
@@ -59082,47 +59083,47 @@
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV303" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ303" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA303" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB303" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC303" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -59154,12 +59155,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -59208,7 +59209,7 @@
       </c>
       <c r="U304" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -59233,7 +59234,7 @@
       </c>
       <c r="AS304" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT304" t="n">
@@ -59246,42 +59247,42 @@
       </c>
       <c r="AV304" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ304" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA304" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB304" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC304" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -59313,12 +59314,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -59359,22 +59360,22 @@
       </c>
       <c r="U305" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V305" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W305" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_KR_KDCA</t>
         </is>
       </c>
       <c r="X305" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>파라티푸스</t>
         </is>
       </c>
       <c r="Y305" t="inlineStr">
@@ -59384,7 +59385,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -59399,7 +59400,7 @@
       </c>
       <c r="AC305" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:KR:national</t>
         </is>
       </c>
       <c r="AD305" t="inlineStr">
@@ -59434,17 +59435,17 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>KR_KDCA_current</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+          <t>Korea KDCA paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM305" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN305" t="b">
@@ -59467,7 +59468,7 @@
       </c>
       <c r="AS305" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT305" t="n">
@@ -59480,42 +59481,834 @@
       </c>
       <c r="AV305" t="inlineStr">
         <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW305" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX305" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY305" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA305" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB305" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC305" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N306" t="n">
+        <v>0</v>
+      </c>
+      <c r="O306" t="n">
+        <v>0</v>
+      </c>
+      <c r="R306" t="n">
+        <v>0</v>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO306" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP306" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ306" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS306" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT306" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU306" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV306" t="inlineStr">
+        <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW305" t="inlineStr">
+      <c r="AW306" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX305" t="inlineStr">
+      <c r="AX306" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY305" t="inlineStr">
+      <c r="AY306" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ305" t="inlineStr">
+      <c r="AZ306" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA305" t="inlineStr">
+      <c r="BA306" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB305" t="inlineStr">
+      <c r="BB306" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC305" t="inlineStr">
+      <c r="BC306" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N307" t="n">
+        <v>0</v>
+      </c>
+      <c r="O307" t="n">
+        <v>0</v>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W307" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X307" t="inlineStr">
+        <is>
+          <t>Paratyfoidfeber</t>
+        </is>
+      </c>
+      <c r="Y307" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z307" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB307" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC307" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD307" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE307" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF307" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG307" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH307" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI307" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ307" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK307" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+        </is>
+      </c>
+      <c r="AM307" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN307" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO307" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP307" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ307" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS307" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_705_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT307" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU307" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV307" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW307" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX307" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY307" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ307" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA307" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB307" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC307" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N308" t="n">
+        <v>1</v>
+      </c>
+      <c r="O308" t="n">
+        <v>1</v>
+      </c>
+      <c r="P308" t="n">
+        <v>1</v>
+      </c>
+      <c r="R308" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO308" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP308" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ308" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS308" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT308" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU308" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV308" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW308" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX308" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY308" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ308" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA308" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB308" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC308" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N309" t="n">
+        <v>1</v>
+      </c>
+      <c r="O309" t="n">
+        <v>1</v>
+      </c>
+      <c r="P309" t="n">
+        <v>1</v>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W309" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X309" t="inlineStr">
+        <is>
+          <t>Salmonella Paratyphi infection</t>
+        </is>
+      </c>
+      <c r="Y309" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z309" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB309" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC309" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD309" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE309" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF309" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG309" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH309" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI309" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ309" t="inlineStr">
+        <is>
+          <t>US_NNDSS_Paratyphi_current</t>
+        </is>
+      </c>
+      <c r="AK309" t="inlineStr">
+        <is>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
+        </is>
+      </c>
+      <c r="AM309" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN309" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO309" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP309" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ309" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS309" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT309" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU309" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV309" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW309" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX309" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY309" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ309" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA309" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB309" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC309" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -59552,7 +60345,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
@@ -59635,7 +60428,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10">
@@ -59645,7 +60438,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11">
@@ -59665,7 +60458,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13">
@@ -59697,7 +60490,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -60702,6 +60702,405 @@
         </is>
       </c>
     </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N312" t="n">
+        <v>0</v>
+      </c>
+      <c r="O312" t="n">
+        <v>0</v>
+      </c>
+      <c r="P312" t="n">
+        <v>0</v>
+      </c>
+      <c r="R312" t="n">
+        <v>0</v>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA312" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO312" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP312" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ312" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS312" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT312" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU312" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV312" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW312" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX312" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY312" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ312" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA312" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB312" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC312" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N313" t="n">
+        <v>0</v>
+      </c>
+      <c r="O313" t="n">
+        <v>0</v>
+      </c>
+      <c r="P313" t="n">
+        <v>0</v>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W313" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X313" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="Y313" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z313" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA313" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB313" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC313" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD313" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE313" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF313" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG313" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH313" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI313" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ313" t="inlineStr">
+        <is>
+          <t>JP_NIID_current</t>
+        </is>
+      </c>
+      <c r="AK313" t="inlineStr">
+        <is>
+          <t>Japan NIID paratyphoid-only notifications.</t>
+        </is>
+      </c>
+      <c r="AM313" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN313" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO313" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP313" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ313" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS313" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT313" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU313" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV313" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW313" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX313" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY313" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA313" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB313" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC313" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -60735,7 +61134,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -60818,7 +61217,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10">
@@ -60828,7 +61227,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -60848,7 +61247,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -53603,12 +53603,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -53642,13 +53642,13 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O276" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R276" t="n">
-        <v>0.03737952171313338</v>
+        <v>0</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -53657,7 +53657,7 @@
       </c>
       <c r="U276" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -53682,7 +53682,7 @@
       </c>
       <c r="AS276" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT276" t="n">
@@ -53695,42 +53695,42 @@
       </c>
       <c r="AV276" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA276" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB276" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC276" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -53762,12 +53762,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -53801,29 +53801,29 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O277" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U277" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V277" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W277" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X277" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y277" t="inlineStr">
@@ -53833,7 +53833,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -53848,7 +53848,7 @@
       </c>
       <c r="AC277" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD277" t="inlineStr">
@@ -53883,17 +53883,17 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Paratyphoid-only source category.</t>
+          <t>New Zealand PHF Science paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -53916,7 +53916,7 @@
       </c>
       <c r="AS277" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT277" t="n">
@@ -53929,42 +53929,42 @@
       </c>
       <c r="AV277" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA277" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB277" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC277" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -53996,12 +53996,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -54035,16 +54035,13 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O278" t="n">
-        <v>1</v>
-      </c>
-      <c r="P278" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R278" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.03737952171313338</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
@@ -54053,12 +54050,12 @@
       </c>
       <c r="U278" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO278" t="inlineStr">
@@ -54078,7 +54075,7 @@
       </c>
       <c r="AS278" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT278" t="n">
@@ -54091,42 +54088,42 @@
       </c>
       <c r="AV278" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -54158,12 +54155,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -54197,32 +54194,29 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O279" t="n">
-        <v>1</v>
-      </c>
-      <c r="P279" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U279" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="V279" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="W279" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X279" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi infection</t>
+          <t>Paratyfoidfeber</t>
         </is>
       </c>
       <c r="Y279" t="inlineStr">
@@ -54232,12 +54226,12 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB279" t="inlineStr">
@@ -54247,7 +54241,7 @@
       </c>
       <c r="AC279" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD279" t="inlineStr">
@@ -54282,17 +54276,17 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>US_NNDSS_Paratyphi_current</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
         <is>
-          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Paratyphoid-only source category.</t>
         </is>
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -54315,7 +54309,7 @@
       </c>
       <c r="AS279" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT279" t="n">
@@ -54328,42 +54322,42 @@
       </c>
       <c r="AV279" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA279" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB279" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC279" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -54395,12 +54389,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -54425,7 +54419,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -54434,16 +54428,16 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P280" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R280" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S280" t="inlineStr">
         <is>
@@ -54452,7 +54446,7 @@
       </c>
       <c r="U280" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
@@ -54462,7 +54456,7 @@
       </c>
       <c r="AO280" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP280" t="inlineStr">
@@ -54472,12 +54466,12 @@
       </c>
       <c r="AQ280" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS280" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT280" t="n">
@@ -54485,47 +54479,47 @@
       </c>
       <c r="AU280" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV280" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA280" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB280" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC280" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -54557,12 +54551,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -54587,7 +54581,7 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
@@ -54596,32 +54590,32 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U281" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="V281" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="W281" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X281" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Salmonella Paratyphi infection</t>
         </is>
       </c>
       <c r="Y281" t="inlineStr">
@@ -54646,7 +54640,7 @@
       </c>
       <c r="AC281" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD281" t="inlineStr">
@@ -54681,12 +54675,12 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>US_NNDSS_Paratyphi_current</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
         </is>
       </c>
       <c r="AM281" t="inlineStr">
@@ -54699,7 +54693,7 @@
       </c>
       <c r="AO281" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP281" t="inlineStr">
@@ -54709,12 +54703,12 @@
       </c>
       <c r="AQ281" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS281" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT281" t="n">
@@ -54722,47 +54716,47 @@
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV281" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ281" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA281" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB281" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC281" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -54794,12 +54788,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -54833,93 +54827,98 @@
         </is>
       </c>
       <c r="N282" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" t="n">
+        <v>0</v>
+      </c>
+      <c r="P282" t="n">
+        <v>0</v>
+      </c>
+      <c r="R282" t="n">
+        <v>0</v>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP282" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ282" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT282" t="n">
         <v>1</v>
       </c>
-      <c r="O282" t="n">
-        <v>1</v>
-      </c>
-      <c r="P282" t="n">
-        <v>1</v>
-      </c>
-      <c r="R282" t="n">
-        <v>0.01693265755097047</v>
-      </c>
-      <c r="S282" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA282" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO282" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP282" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ282" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS282" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
-        </is>
-      </c>
-      <c r="AT282" t="n">
-        <v>2</v>
-      </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV282" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ282" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA282" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB282" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC282" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -54951,12 +54950,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -54990,32 +54989,32 @@
         </is>
       </c>
       <c r="N283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U283" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V283" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W283" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X283" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y283" t="inlineStr">
@@ -55025,7 +55024,7 @@
       </c>
       <c r="Z283" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
@@ -55040,7 +55039,7 @@
       </c>
       <c r="AC283" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD283" t="inlineStr">
@@ -55075,17 +55074,17 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM283" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN283" t="b">
@@ -55093,70 +55092,70 @@
       </c>
       <c r="AO283" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP283" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ283" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS283" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT283" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV283" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ283" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA283" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB283" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC283" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55188,12 +55187,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -55218,7 +55217,7 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
@@ -55227,27 +55226,22 @@
         </is>
       </c>
       <c r="N284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R284" t="n">
-        <v>0</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S284" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U284" t="inlineStr">
-        <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA284" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -55255,70 +55249,70 @@
       </c>
       <c r="AO284" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP284" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ284" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS284" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT284" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU284" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV284" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW284" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ284" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA284" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB284" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC284" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -55350,12 +55344,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -55380,7 +55374,7 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
@@ -55389,32 +55383,32 @@
         </is>
       </c>
       <c r="N285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U285" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="V285" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="W285" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X285" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y285" t="inlineStr">
@@ -55424,7 +55418,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -55439,7 +55433,7 @@
       </c>
       <c r="AC285" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD285" t="inlineStr">
@@ -55474,17 +55468,17 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -55492,70 +55486,70 @@
       </c>
       <c r="AO285" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP285" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ285" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS285" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT285" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV285" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ285" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA285" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB285" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC285" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -55587,12 +55581,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -55642,6 +55636,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA286" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -55649,70 +55648,70 @@
       </c>
       <c r="AO286" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP286" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ286" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS286" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT286" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV286" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW286" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ286" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA286" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB286" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC286" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55744,12 +55743,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -55793,22 +55792,22 @@
       </c>
       <c r="U287" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V287" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W287" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X287" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y287" t="inlineStr">
@@ -55818,7 +55817,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -55833,7 +55832,7 @@
       </c>
       <c r="AC287" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD287" t="inlineStr">
@@ -55868,17 +55867,17 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN287" t="b">
@@ -55886,70 +55885,70 @@
       </c>
       <c r="AO287" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP287" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ287" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS287" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT287" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV287" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW287" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ287" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA287" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB287" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC287" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55981,12 +55980,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -56011,7 +56010,7 @@
       </c>
       <c r="L288" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M288" t="inlineStr">
@@ -56020,98 +56019,93 @@
         </is>
       </c>
       <c r="N288" t="n">
+        <v>0</v>
+      </c>
+      <c r="O288" t="n">
+        <v>0</v>
+      </c>
+      <c r="P288" t="n">
+        <v>0</v>
+      </c>
+      <c r="R288" t="n">
+        <v>0</v>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO288" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP288" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ288" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS288" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT288" t="n">
         <v>2</v>
       </c>
-      <c r="O288" t="n">
-        <v>2</v>
-      </c>
-      <c r="P288" t="n">
-        <v>2</v>
-      </c>
-      <c r="R288" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S288" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U288" t="inlineStr">
-        <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA288" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO288" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP288" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ288" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS288" t="inlineStr">
-        <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT288" t="n">
-        <v>1</v>
-      </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV288" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ288" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA288" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB288" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC288" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -56143,12 +56137,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -56173,7 +56167,7 @@
       </c>
       <c r="L289" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M289" t="inlineStr">
@@ -56182,32 +56176,32 @@
         </is>
       </c>
       <c r="N289" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O289" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P289" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U289" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="V289" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="W289" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X289" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi infection</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y289" t="inlineStr">
@@ -56217,7 +56211,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -56232,7 +56226,7 @@
       </c>
       <c r="AC289" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD289" t="inlineStr">
@@ -56267,17 +56261,17 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>US_NNDSS_Paratyphi_current</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
         <is>
-          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN289" t="b">
@@ -56290,7 +56284,7 @@
       </c>
       <c r="AP289" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ289" t="inlineStr">
@@ -56300,55 +56294,55 @@
       </c>
       <c r="AS289" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT289" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU289" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV289" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW289" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ289" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA289" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB289" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC289" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -56380,12 +56374,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -56410,7 +56404,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -56419,16 +56413,16 @@
         </is>
       </c>
       <c r="N290" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O290" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P290" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R290" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S290" t="inlineStr">
         <is>
@@ -56437,7 +56431,7 @@
       </c>
       <c r="U290" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AA290" t="inlineStr">
@@ -56447,7 +56441,7 @@
       </c>
       <c r="AO290" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP290" t="inlineStr">
@@ -56457,12 +56451,12 @@
       </c>
       <c r="AQ290" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS290" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT290" t="n">
@@ -56470,47 +56464,47 @@
       </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV290" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW290" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX290" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY290" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ290" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA290" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB290" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC290" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -56542,12 +56536,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -56572,7 +56566,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -56581,32 +56575,32 @@
         </is>
       </c>
       <c r="N291" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O291" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P291" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U291" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="V291" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="W291" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X291" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Salmonella Paratyphi infection</t>
         </is>
       </c>
       <c r="Y291" t="inlineStr">
@@ -56631,7 +56625,7 @@
       </c>
       <c r="AC291" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD291" t="inlineStr">
@@ -56666,12 +56660,12 @@
       </c>
       <c r="AJ291" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>US_NNDSS_Paratyphi_current</t>
         </is>
       </c>
       <c r="AK291" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
         </is>
       </c>
       <c r="AM291" t="inlineStr">
@@ -56684,7 +56678,7 @@
       </c>
       <c r="AO291" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP291" t="inlineStr">
@@ -56694,12 +56688,12 @@
       </c>
       <c r="AQ291" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS291" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT291" t="n">
@@ -56707,47 +56701,47 @@
       </c>
       <c r="AU291" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV291" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW291" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX291" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY291" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ291" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA291" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB291" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC291" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -56779,12 +56773,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -56834,6 +56828,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA292" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -56841,70 +56840,70 @@
       </c>
       <c r="AO292" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP292" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ292" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS292" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT292" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU292" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV292" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW292" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX292" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY292" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ292" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA292" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB292" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC292" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56936,12 +56935,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -56985,22 +56984,22 @@
       </c>
       <c r="U293" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V293" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W293" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X293" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y293" t="inlineStr">
@@ -57010,7 +57009,7 @@
       </c>
       <c r="Z293" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA293" t="inlineStr">
@@ -57025,7 +57024,7 @@
       </c>
       <c r="AC293" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD293" t="inlineStr">
@@ -57060,17 +57059,17 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM293" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN293" t="b">
@@ -57078,70 +57077,70 @@
       </c>
       <c r="AO293" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP293" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ293" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS293" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT293" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU293" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV293" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW293" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX293" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY293" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ293" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA293" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB293" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC293" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -57173,12 +57172,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -57203,7 +57202,7 @@
       </c>
       <c r="L294" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M294" t="inlineStr">
@@ -57228,11 +57227,6 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U294" t="inlineStr">
-        <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA294" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -57240,70 +57234,70 @@
       </c>
       <c r="AO294" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP294" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ294" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS294" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT294" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU294" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV294" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW294" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX294" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY294" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ294" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA294" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB294" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC294" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -57335,12 +57329,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -57365,7 +57359,7 @@
       </c>
       <c r="L295" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M295" t="inlineStr">
@@ -57384,22 +57378,22 @@
       </c>
       <c r="U295" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="V295" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="W295" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X295" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y295" t="inlineStr">
@@ -57409,7 +57403,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -57424,7 +57418,7 @@
       </c>
       <c r="AC295" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD295" t="inlineStr">
@@ -57459,17 +57453,17 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN295" t="b">
@@ -57477,70 +57471,70 @@
       </c>
       <c r="AO295" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP295" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ295" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS295" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT295" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU295" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV295" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW295" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX295" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY295" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ295" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA295" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB295" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC295" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -57572,12 +57566,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -57627,6 +57621,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA296" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -57634,70 +57633,70 @@
       </c>
       <c r="AO296" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP296" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ296" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS296" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT296" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU296" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV296" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW296" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX296" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY296" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ296" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA296" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB296" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC296" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -57729,12 +57728,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -57778,22 +57777,22 @@
       </c>
       <c r="U297" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V297" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W297" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X297" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y297" t="inlineStr">
@@ -57803,7 +57802,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
@@ -57818,7 +57817,7 @@
       </c>
       <c r="AC297" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD297" t="inlineStr">
@@ -57853,17 +57852,17 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -57871,70 +57870,70 @@
       </c>
       <c r="AO297" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP297" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ297" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS297" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT297" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU297" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV297" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW297" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX297" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY297" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ297" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA297" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB297" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC297" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -57966,12 +57965,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -57996,7 +57995,7 @@
       </c>
       <c r="L298" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M298" t="inlineStr">
@@ -58005,27 +58004,22 @@
         </is>
       </c>
       <c r="N298" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O298" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P298" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R298" t="n">
-        <v>0.002450425222697299</v>
+        <v>0</v>
       </c>
       <c r="S298" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U298" t="inlineStr">
-        <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA298" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -58033,70 +58027,70 @@
       </c>
       <c r="AO298" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP298" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ298" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS298" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT298" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV298" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW298" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ298" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA298" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB298" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC298" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -58128,12 +58122,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -58158,7 +58152,7 @@
       </c>
       <c r="L299" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M299" t="inlineStr">
@@ -58167,32 +58161,32 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O299" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P299" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U299" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="W299" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X299" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y299" t="inlineStr">
@@ -58202,7 +58196,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -58217,7 +58211,7 @@
       </c>
       <c r="AC299" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD299" t="inlineStr">
@@ -58252,17 +58246,17 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN299" t="b">
@@ -58270,70 +58264,70 @@
       </c>
       <c r="AO299" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP299" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ299" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS299" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT299" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV299" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW299" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ299" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA299" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB299" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC299" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -58365,12 +58359,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -58404,22 +58398,27 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O300" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P300" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R300" t="n">
-        <v>0</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S300" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA300" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -58427,70 +58426,70 @@
       </c>
       <c r="AO300" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP300" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ300" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS300" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT300" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV300" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW300" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX300" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY300" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ300" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA300" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB300" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC300" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -58522,12 +58521,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -58561,32 +58560,32 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O301" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P301" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U301" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V301" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W301" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X301" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y301" t="inlineStr">
@@ -58596,7 +58595,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -58611,7 +58610,7 @@
       </c>
       <c r="AC301" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD301" t="inlineStr">
@@ -58646,17 +58645,17 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -58664,70 +58663,70 @@
       </c>
       <c r="AO301" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP301" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ301" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS301" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT301" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV301" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW301" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ301" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA301" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB301" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC301" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -58759,12 +58758,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -58789,12 +58788,12 @@
       </c>
       <c r="L302" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N302" t="n">
@@ -58803,6 +58802,9 @@
       <c r="O302" t="n">
         <v>0</v>
       </c>
+      <c r="P302" t="n">
+        <v>0</v>
+      </c>
       <c r="R302" t="n">
         <v>0</v>
       </c>
@@ -58811,82 +58813,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U302" t="inlineStr">
-        <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
-        </is>
-      </c>
       <c r="AA302" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO302" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP302" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ302" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS302" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT302" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV302" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW302" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ302" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA302" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB302" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC302" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -58918,12 +58915,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -58948,12 +58945,12 @@
       </c>
       <c r="L303" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N303" t="n">
@@ -58962,19 +58959,22 @@
       <c r="O303" t="n">
         <v>0</v>
       </c>
+      <c r="P303" t="n">
+        <v>0</v>
+      </c>
       <c r="U303" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="V303" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="W303" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X303" t="inlineStr">
@@ -58989,12 +58989,12 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB303" t="inlineStr">
@@ -59004,7 +59004,7 @@
       </c>
       <c r="AC303" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD303" t="inlineStr">
@@ -59039,17 +59039,17 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>AU_NINDSS_current</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
         <is>
-          <t>Australia NINDSS paratyphoid-only notifications; excludes typhoid fever.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN303" t="b">
@@ -59057,70 +59057,70 @@
       </c>
       <c r="AO303" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP303" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ303" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS303" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT303" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV303" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ303" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA303" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB303" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC303" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -59152,12 +59152,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -59206,7 +59206,7 @@
       </c>
       <c r="U304" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA304" t="inlineStr">
@@ -59216,7 +59216,7 @@
       </c>
       <c r="AO304" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP304" t="inlineStr">
@@ -59226,12 +59226,12 @@
       </c>
       <c r="AQ304" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS304" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT304" t="n">
@@ -59239,47 +59239,47 @@
       </c>
       <c r="AU304" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV304" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ304" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA304" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB304" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC304" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -59311,12 +59311,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -59357,22 +59357,22 @@
       </c>
       <c r="U305" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V305" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W305" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_AU_NINDSS</t>
         </is>
       </c>
       <c r="X305" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y305" t="inlineStr">
@@ -59382,7 +59382,7 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
@@ -59397,7 +59397,7 @@
       </c>
       <c r="AC305" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:AU:national</t>
         </is>
       </c>
       <c r="AD305" t="inlineStr">
@@ -59432,17 +59432,17 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>AU_NINDSS_current</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
+          <t>Australia NINDSS paratyphoid-only notifications; excludes typhoid fever.</t>
         </is>
       </c>
       <c r="AM305" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN305" t="b">
@@ -59450,7 +59450,7 @@
       </c>
       <c r="AO305" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP305" t="inlineStr">
@@ -59460,12 +59460,12 @@
       </c>
       <c r="AQ305" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS305" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT305" t="n">
@@ -59473,47 +59473,47 @@
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV305" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW305" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ305" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA305" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB305" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC305" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -59545,12 +59545,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -59599,7 +59599,7 @@
       </c>
       <c r="U306" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -59619,12 +59619,12 @@
       </c>
       <c r="AQ306" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS306" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AT306" t="n">
@@ -59632,47 +59632,47 @@
       </c>
       <c r="AU306" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV306" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW306" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ306" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA306" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB306" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC306" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -59704,12 +59704,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -59750,22 +59750,22 @@
       </c>
       <c r="U307" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="V307" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="W307" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X307" t="inlineStr">
         <is>
-          <t>파라티푸스</t>
+          <t>Salmonella Paratyphi</t>
         </is>
       </c>
       <c r="Y307" t="inlineStr">
@@ -59775,7 +59775,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -59790,7 +59790,7 @@
       </c>
       <c r="AC307" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD307" t="inlineStr">
@@ -59825,12 +59825,12 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>KR_KDCA_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
         <is>
-          <t>Korea KDCA paratyphoid-only notifications.</t>
+          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
         </is>
       </c>
       <c r="AM307" t="inlineStr">
@@ -59853,12 +59853,12 @@
       </c>
       <c r="AQ307" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS307" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AT307" t="n">
@@ -59866,47 +59866,47 @@
       </c>
       <c r="AU307" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV307" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW307" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ307" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA307" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB307" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC307" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -59938,12 +59938,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -59992,7 +59992,7 @@
       </c>
       <c r="U308" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -60017,7 +60017,7 @@
       </c>
       <c r="AS308" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT308" t="n">
@@ -60030,42 +60030,42 @@
       </c>
       <c r="AV308" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ308" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA308" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB308" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC308" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -60097,12 +60097,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -60143,22 +60143,22 @@
       </c>
       <c r="U309" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V309" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W309" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_KR_KDCA</t>
         </is>
       </c>
       <c r="X309" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>파라티푸스</t>
         </is>
       </c>
       <c r="Y309" t="inlineStr">
@@ -60168,7 +60168,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -60183,7 +60183,7 @@
       </c>
       <c r="AC309" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:KR:national</t>
         </is>
       </c>
       <c r="AD309" t="inlineStr">
@@ -60218,17 +60218,17 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>KR_KDCA_current</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+          <t>Korea KDCA paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM309" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN309" t="b">
@@ -60251,7 +60251,7 @@
       </c>
       <c r="AS309" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT309" t="n">
@@ -60264,42 +60264,42 @@
       </c>
       <c r="AV309" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ309" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA309" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB309" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC309" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -60331,12 +60331,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -60361,7 +60361,7 @@
       </c>
       <c r="L310" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M310" t="inlineStr">
@@ -60370,16 +60370,13 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O310" t="n">
-        <v>1</v>
-      </c>
-      <c r="P310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R310" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S310" t="inlineStr">
         <is>
@@ -60388,12 +60385,12 @@
       </c>
       <c r="U310" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO310" t="inlineStr">
@@ -60413,7 +60410,7 @@
       </c>
       <c r="AS310" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AT310" t="n">
@@ -60426,42 +60423,42 @@
       </c>
       <c r="AV310" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ310" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA310" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB310" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC310" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -60493,12 +60490,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -60523,7 +60520,7 @@
       </c>
       <c r="L311" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M311" t="inlineStr">
@@ -60532,32 +60529,29 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O311" t="n">
-        <v>1</v>
-      </c>
-      <c r="P311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U311" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="V311" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="W311" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X311" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi infection</t>
+          <t>Paratyfoidfeber</t>
         </is>
       </c>
       <c r="Y311" t="inlineStr">
@@ -60567,12 +60561,12 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB311" t="inlineStr">
@@ -60582,7 +60576,7 @@
       </c>
       <c r="AC311" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD311" t="inlineStr">
@@ -60617,17 +60611,17 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>US_NNDSS_Paratyphi_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
         <is>
-          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
         </is>
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN311" t="b">
@@ -60650,7 +60644,7 @@
       </c>
       <c r="AS311" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AT311" t="n">
@@ -60663,42 +60657,42 @@
       </c>
       <c r="AV311" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ311" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA311" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB311" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC311" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -60730,12 +60724,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -60760,7 +60754,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -60769,16 +60763,16 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R312" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S312" t="inlineStr">
         <is>
@@ -60787,7 +60781,7 @@
       </c>
       <c r="U312" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -60797,7 +60791,7 @@
       </c>
       <c r="AO312" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP312" t="inlineStr">
@@ -60807,12 +60801,12 @@
       </c>
       <c r="AQ312" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS312" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT312" t="n">
@@ -60820,47 +60814,47 @@
       </c>
       <c r="AU312" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV312" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ312" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA312" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB312" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC312" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -60892,12 +60886,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -60922,7 +60916,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -60931,32 +60925,32 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U313" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="V313" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="W313" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X313" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Salmonella Paratyphi infection</t>
         </is>
       </c>
       <c r="Y313" t="inlineStr">
@@ -60981,7 +60975,7 @@
       </c>
       <c r="AC313" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD313" t="inlineStr">
@@ -61016,12 +61010,12 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>US_NNDSS_Paratyphi_current</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
         </is>
       </c>
       <c r="AM313" t="inlineStr">
@@ -61034,7 +61028,7 @@
       </c>
       <c r="AO313" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP313" t="inlineStr">
@@ -61044,12 +61038,12 @@
       </c>
       <c r="AQ313" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS313" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT313" t="n">
@@ -61057,45 +61051,444 @@
       </c>
       <c r="AU313" t="inlineStr">
         <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV313" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW313" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX313" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY313" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ313" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA313" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB313" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC313" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N314" t="n">
+        <v>0</v>
+      </c>
+      <c r="O314" t="n">
+        <v>0</v>
+      </c>
+      <c r="P314" t="n">
+        <v>0</v>
+      </c>
+      <c r="R314" t="n">
+        <v>0</v>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA314" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO314" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP314" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ314" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS314" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT314" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU314" t="inlineStr">
+        <is>
           <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
-      <c r="AV313" t="inlineStr">
+      <c r="AV314" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW313" t="inlineStr">
+      <c r="AW314" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX313" t="inlineStr">
+      <c r="AX314" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY313" t="inlineStr">
+      <c r="AY314" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ313" t="inlineStr">
+      <c r="AZ314" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA313" t="inlineStr">
+      <c r="BA314" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB313" t="inlineStr">
+      <c r="BB314" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC313" t="inlineStr">
+      <c r="BC314" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N315" t="n">
+        <v>0</v>
+      </c>
+      <c r="O315" t="n">
+        <v>0</v>
+      </c>
+      <c r="P315" t="n">
+        <v>0</v>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W315" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X315" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="Y315" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z315" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA315" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB315" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC315" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD315" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE315" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF315" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG315" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH315" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI315" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ315" t="inlineStr">
+        <is>
+          <t>JP_NIID_current</t>
+        </is>
+      </c>
+      <c r="AK315" t="inlineStr">
+        <is>
+          <t>Japan NIID paratyphoid-only notifications.</t>
+        </is>
+      </c>
+      <c r="AM315" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN315" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO315" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP315" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ315" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS315" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT315" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU315" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV315" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW315" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX315" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY315" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ315" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA315" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB315" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC315" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -61217,7 +61610,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10">
@@ -61227,7 +61620,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11">
@@ -61247,7 +61640,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -53249,13 +53249,13 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O274" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R274" t="n">
-        <v>0.1061385495477304</v>
+        <v>0.1238283078056854</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -53408,10 +53408,10 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O275" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U275" t="inlineStr">
         <is>
@@ -61672,7 +61672,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -61494,6 +61494,799 @@
         </is>
       </c>
     </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N316" t="n">
+        <v>0</v>
+      </c>
+      <c r="O316" t="n">
+        <v>0</v>
+      </c>
+      <c r="P316" t="n">
+        <v>0</v>
+      </c>
+      <c r="R316" t="n">
+        <v>0</v>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA316" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO316" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP316" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ316" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS316" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT316" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU316" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV316" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW316" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX316" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY316" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ316" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA316" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB316" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC316" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N317" t="n">
+        <v>0</v>
+      </c>
+      <c r="O317" t="n">
+        <v>0</v>
+      </c>
+      <c r="P317" t="n">
+        <v>0</v>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="W317" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X317" t="inlineStr">
+        <is>
+          <t>Paratyphoid</t>
+        </is>
+      </c>
+      <c r="Y317" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA317" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB317" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC317" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD317" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE317" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF317" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG317" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH317" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI317" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ317" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK317" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM317" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN317" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO317" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP317" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ317" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS317" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT317" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU317" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV317" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW317" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX317" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY317" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ317" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA317" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB317" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC317" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N318" t="n">
+        <v>1</v>
+      </c>
+      <c r="O318" t="n">
+        <v>1</v>
+      </c>
+      <c r="P318" t="n">
+        <v>1</v>
+      </c>
+      <c r="R318" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA318" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO318" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP318" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ318" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS318" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT318" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU318" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV318" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW318" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX318" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY318" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ318" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA318" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB318" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC318" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N319" t="n">
+        <v>1</v>
+      </c>
+      <c r="O319" t="n">
+        <v>1</v>
+      </c>
+      <c r="P319" t="n">
+        <v>1</v>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>Salmonella Paratyphi infection</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB319" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC319" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD319" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE319" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF319" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG319" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH319" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI319" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ319" t="inlineStr">
+        <is>
+          <t>US_NNDSS_Paratyphi_current</t>
+        </is>
+      </c>
+      <c r="AK319" t="inlineStr">
+        <is>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
+        </is>
+      </c>
+      <c r="AM319" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN319" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO319" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP319" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ319" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS319" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT319" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU319" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV319" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW319" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX319" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY319" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA319" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB319" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC319" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -61527,7 +62320,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -61610,7 +62403,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10">
@@ -61620,7 +62413,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="11">
@@ -61640,7 +62433,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
@@ -61672,7 +62465,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -51218,13 +51218,13 @@
         </is>
       </c>
       <c r="N262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O262" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R262" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.007345623639039581</v>
       </c>
       <c r="S262" t="inlineStr">
         <is>
@@ -51377,10 +51377,10 @@
         </is>
       </c>
       <c r="N263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O263" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U263" t="inlineStr">
         <is>
@@ -52817,12 +52817,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -52856,13 +52856,13 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R272" t="n">
-        <v>0</v>
+        <v>0.01355270280196709</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -52871,7 +52871,7 @@
       </c>
       <c r="U272" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -52881,7 +52881,7 @@
       </c>
       <c r="AO272" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP272" t="inlineStr">
@@ -52891,12 +52891,12 @@
       </c>
       <c r="AQ272" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS272" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT272" t="n">
@@ -52904,47 +52904,47 @@
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA272" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB272" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC272" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -52976,12 +52976,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -53015,29 +53015,29 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U273" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V273" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W273" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_HK_CHP</t>
         </is>
       </c>
       <c r="X273" t="inlineStr">
         <is>
-          <t>파라티푸스</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y273" t="inlineStr">
@@ -53062,7 +53062,7 @@
       </c>
       <c r="AC273" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:HK:national</t>
         </is>
       </c>
       <c r="AD273" t="inlineStr">
@@ -53097,12 +53097,12 @@
       </c>
       <c r="AJ273" t="inlineStr">
         <is>
-          <t>KR_KDCA_current</t>
+          <t>HK_CHP_current</t>
         </is>
       </c>
       <c r="AK273" t="inlineStr">
         <is>
-          <t>Korea KDCA paratyphoid-only notifications.</t>
+          <t>Hong Kong, China CHP paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM273" t="inlineStr">
@@ -53115,7 +53115,7 @@
       </c>
       <c r="AO273" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP273" t="inlineStr">
@@ -53125,12 +53125,12 @@
       </c>
       <c r="AQ273" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS273" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT273" t="n">
@@ -53138,47 +53138,47 @@
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV273" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA273" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB273" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC273" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -53210,12 +53210,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -53249,13 +53249,13 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O274" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R274" t="n">
-        <v>0.1238283078056854</v>
+        <v>0</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
       </c>
       <c r="U274" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA274" t="inlineStr">
@@ -53289,7 +53289,7 @@
       </c>
       <c r="AS274" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT274" t="n">
@@ -53302,42 +53302,42 @@
       </c>
       <c r="AV274" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA274" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB274" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC274" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -53369,12 +53369,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -53408,29 +53408,29 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O275" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="U275" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V275" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W275" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_KR_KDCA</t>
         </is>
       </c>
       <c r="X275" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>파라티푸스</t>
         </is>
       </c>
       <c r="Y275" t="inlineStr">
@@ -53440,7 +53440,7 @@
       </c>
       <c r="Z275" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA275" t="inlineStr">
@@ -53455,7 +53455,7 @@
       </c>
       <c r="AC275" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:KR:national</t>
         </is>
       </c>
       <c r="AD275" t="inlineStr">
@@ -53490,17 +53490,17 @@
       </c>
       <c r="AJ275" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>KR_KDCA_current</t>
         </is>
       </c>
       <c r="AK275" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+          <t>Korea KDCA paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM275" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN275" t="b">
@@ -53523,7 +53523,7 @@
       </c>
       <c r="AS275" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT275" t="n">
@@ -53536,42 +53536,42 @@
       </c>
       <c r="AV275" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA275" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB275" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC275" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -53603,12 +53603,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -53642,13 +53642,13 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O276" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R276" t="n">
-        <v>0</v>
+        <v>0.1238283078056854</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -53657,7 +53657,7 @@
       </c>
       <c r="U276" t="inlineStr">
         <is>
-          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AA276" t="inlineStr">
@@ -53682,7 +53682,7 @@
       </c>
       <c r="AS276" t="inlineStr">
         <is>
-          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AT276" t="n">
@@ -53695,42 +53695,42 @@
       </c>
       <c r="AV276" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA276" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB276" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC276" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -53762,12 +53762,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -53801,29 +53801,29 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O277" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U277" t="inlineStr">
         <is>
-          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="V277" t="inlineStr">
         <is>
-          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="W277" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X277" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Paratyfoidfeber</t>
         </is>
       </c>
       <c r="Y277" t="inlineStr">
@@ -53833,7 +53833,7 @@
       </c>
       <c r="Z277" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA277" t="inlineStr">
@@ -53848,7 +53848,7 @@
       </c>
       <c r="AC277" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD277" t="inlineStr">
@@ -53883,17 +53883,17 @@
       </c>
       <c r="AJ277" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK277" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science paratyphoid-only notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
         </is>
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -53916,7 +53916,7 @@
       </c>
       <c r="AS277" t="inlineStr">
         <is>
-          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AT277" t="n">
@@ -53929,42 +53929,42 @@
       </c>
       <c r="AV277" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA277" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB277" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC277" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -53996,12 +53996,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -54035,13 +54035,13 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O278" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R278" t="n">
-        <v>0.03737952171313338</v>
+        <v>0</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
@@ -54050,7 +54050,7 @@
       </c>
       <c r="U278" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA278" t="inlineStr">
@@ -54075,7 +54075,7 @@
       </c>
       <c r="AS278" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT278" t="n">
@@ -54088,42 +54088,42 @@
       </c>
       <c r="AV278" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -54155,12 +54155,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -54194,29 +54194,29 @@
         </is>
       </c>
       <c r="N279" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O279" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U279" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V279" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W279" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X279" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y279" t="inlineStr">
@@ -54226,7 +54226,7 @@
       </c>
       <c r="Z279" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA279" t="inlineStr">
@@ -54241,7 +54241,7 @@
       </c>
       <c r="AC279" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD279" t="inlineStr">
@@ -54276,17 +54276,17 @@
       </c>
       <c r="AJ279" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK279" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Paratyphoid-only source category.</t>
+          <t>New Zealand PHF Science paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM279" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN279" t="b">
@@ -54309,7 +54309,7 @@
       </c>
       <c r="AS279" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT279" t="n">
@@ -54322,42 +54322,42 @@
       </c>
       <c r="AV279" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA279" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB279" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC279" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -54389,12 +54389,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -54428,16 +54428,13 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O280" t="n">
-        <v>1</v>
-      </c>
-      <c r="P280" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R280" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.03737952171313338</v>
       </c>
       <c r="S280" t="inlineStr">
         <is>
@@ -54446,12 +54443,12 @@
       </c>
       <c r="U280" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AA280" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO280" t="inlineStr">
@@ -54471,7 +54468,7 @@
       </c>
       <c r="AS280" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT280" t="n">
@@ -54484,42 +54481,42 @@
       </c>
       <c r="AV280" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA280" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB280" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC280" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -54551,12 +54548,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -54590,32 +54587,29 @@
         </is>
       </c>
       <c r="N281" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O281" t="n">
-        <v>1</v>
-      </c>
-      <c r="P281" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U281" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="V281" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="W281" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X281" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi infection</t>
+          <t>Paratyfoidfeber</t>
         </is>
       </c>
       <c r="Y281" t="inlineStr">
@@ -54625,12 +54619,12 @@
       </c>
       <c r="Z281" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA281" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB281" t="inlineStr">
@@ -54640,7 +54634,7 @@
       </c>
       <c r="AC281" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD281" t="inlineStr">
@@ -54675,17 +54669,17 @@
       </c>
       <c r="AJ281" t="inlineStr">
         <is>
-          <t>US_NNDSS_Paratyphi_current</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK281" t="inlineStr">
         <is>
-          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Paratyphoid-only source category.</t>
         </is>
       </c>
       <c r="AM281" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN281" t="b">
@@ -54708,7 +54702,7 @@
       </c>
       <c r="AS281" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT281" t="n">
@@ -54721,42 +54715,42 @@
       </c>
       <c r="AV281" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ281" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA281" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB281" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC281" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -54788,12 +54782,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -54818,7 +54812,7 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
@@ -54827,16 +54821,16 @@
         </is>
       </c>
       <c r="N282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R282" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S282" t="inlineStr">
         <is>
@@ -54845,7 +54839,7 @@
       </c>
       <c r="U282" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AA282" t="inlineStr">
@@ -54855,7 +54849,7 @@
       </c>
       <c r="AO282" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP282" t="inlineStr">
@@ -54865,12 +54859,12 @@
       </c>
       <c r="AQ282" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS282" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT282" t="n">
@@ -54878,47 +54872,47 @@
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV282" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ282" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA282" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB282" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC282" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -54950,12 +54944,12 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -54980,7 +54974,7 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
@@ -54989,32 +54983,32 @@
         </is>
       </c>
       <c r="N283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U283" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="V283" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="W283" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X283" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Salmonella Paratyphi infection</t>
         </is>
       </c>
       <c r="Y283" t="inlineStr">
@@ -55039,7 +55033,7 @@
       </c>
       <c r="AC283" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD283" t="inlineStr">
@@ -55074,12 +55068,12 @@
       </c>
       <c r="AJ283" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>US_NNDSS_Paratyphi_current</t>
         </is>
       </c>
       <c r="AK283" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
         </is>
       </c>
       <c r="AM283" t="inlineStr">
@@ -55092,7 +55086,7 @@
       </c>
       <c r="AO283" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP283" t="inlineStr">
@@ -55102,12 +55096,12 @@
       </c>
       <c r="AQ283" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS283" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT283" t="n">
@@ -55115,47 +55109,47 @@
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV283" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ283" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA283" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB283" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC283" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -55187,12 +55181,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -55226,22 +55220,27 @@
         </is>
       </c>
       <c r="N284" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O284" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P284" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R284" t="n">
-        <v>0.01693265755097047</v>
+        <v>0</v>
       </c>
       <c r="S284" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA284" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -55249,70 +55248,70 @@
       </c>
       <c r="AO284" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP284" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ284" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS284" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT284" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU284" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV284" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW284" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ284" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA284" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB284" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC284" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55344,12 +55343,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -55383,32 +55382,32 @@
         </is>
       </c>
       <c r="N285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U285" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V285" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W285" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X285" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y285" t="inlineStr">
@@ -55418,7 +55417,7 @@
       </c>
       <c r="Z285" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA285" t="inlineStr">
@@ -55433,7 +55432,7 @@
       </c>
       <c r="AC285" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD285" t="inlineStr">
@@ -55468,17 +55467,17 @@
       </c>
       <c r="AJ285" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK285" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM285" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN285" t="b">
@@ -55486,70 +55485,70 @@
       </c>
       <c r="AO285" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP285" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ285" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS285" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT285" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV285" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ285" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA285" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB285" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC285" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -55581,12 +55580,12 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -55611,7 +55610,7 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
@@ -55620,27 +55619,22 @@
         </is>
       </c>
       <c r="N286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R286" t="n">
-        <v>0</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S286" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U286" t="inlineStr">
-        <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA286" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -55648,70 +55642,70 @@
       </c>
       <c r="AO286" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP286" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ286" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS286" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT286" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV286" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW286" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ286" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA286" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB286" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC286" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -55743,12 +55737,12 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
@@ -55773,7 +55767,7 @@
       </c>
       <c r="L287" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M287" t="inlineStr">
@@ -55782,32 +55776,32 @@
         </is>
       </c>
       <c r="N287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P287" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U287" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="V287" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="W287" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X287" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y287" t="inlineStr">
@@ -55817,7 +55811,7 @@
       </c>
       <c r="Z287" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA287" t="inlineStr">
@@ -55832,7 +55826,7 @@
       </c>
       <c r="AC287" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD287" t="inlineStr">
@@ -55867,17 +55861,17 @@
       </c>
       <c r="AJ287" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK287" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM287" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN287" t="b">
@@ -55885,70 +55879,70 @@
       </c>
       <c r="AO287" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP287" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ287" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS287" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT287" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU287" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV287" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW287" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX287" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY287" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ287" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA287" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB287" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC287" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -55980,12 +55974,12 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
@@ -56035,6 +56029,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA288" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -56042,70 +56041,70 @@
       </c>
       <c r="AO288" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP288" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ288" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS288" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT288" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU288" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV288" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW288" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX288" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY288" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ288" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA288" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB288" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC288" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56137,12 +56136,12 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
@@ -56186,22 +56185,22 @@
       </c>
       <c r="U289" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V289" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W289" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X289" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y289" t="inlineStr">
@@ -56211,7 +56210,7 @@
       </c>
       <c r="Z289" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA289" t="inlineStr">
@@ -56226,7 +56225,7 @@
       </c>
       <c r="AC289" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD289" t="inlineStr">
@@ -56261,17 +56260,17 @@
       </c>
       <c r="AJ289" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK289" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN289" t="b">
@@ -56279,70 +56278,70 @@
       </c>
       <c r="AO289" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP289" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ289" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS289" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT289" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU289" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV289" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW289" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX289" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY289" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ289" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA289" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB289" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC289" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -56374,12 +56373,12 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
@@ -56404,7 +56403,7 @@
       </c>
       <c r="L290" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M290" t="inlineStr">
@@ -56413,98 +56412,93 @@
         </is>
       </c>
       <c r="N290" t="n">
+        <v>0</v>
+      </c>
+      <c r="O290" t="n">
+        <v>0</v>
+      </c>
+      <c r="P290" t="n">
+        <v>0</v>
+      </c>
+      <c r="R290" t="n">
+        <v>0</v>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO290" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP290" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ290" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS290" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT290" t="n">
         <v>2</v>
       </c>
-      <c r="O290" t="n">
-        <v>2</v>
-      </c>
-      <c r="P290" t="n">
-        <v>2</v>
-      </c>
-      <c r="R290" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S290" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U290" t="inlineStr">
-        <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA290" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO290" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP290" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ290" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS290" t="inlineStr">
-        <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT290" t="n">
-        <v>1</v>
-      </c>
       <c r="AU290" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV290" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW290" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX290" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY290" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ290" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA290" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB290" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC290" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -56536,12 +56530,12 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H291" t="inlineStr">
@@ -56566,7 +56560,7 @@
       </c>
       <c r="L291" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M291" t="inlineStr">
@@ -56575,173 +56569,173 @@
         </is>
       </c>
       <c r="N291" t="n">
+        <v>0</v>
+      </c>
+      <c r="O291" t="n">
+        <v>0</v>
+      </c>
+      <c r="P291" t="n">
+        <v>0</v>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="W291" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X291" t="inlineStr">
+        <is>
+          <t>Paratyphoid</t>
+        </is>
+      </c>
+      <c r="Y291" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z291" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB291" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC291" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD291" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE291" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF291" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG291" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH291" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI291" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ291" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK291" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM291" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN291" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO291" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP291" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ291" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS291" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT291" t="n">
         <v>2</v>
       </c>
-      <c r="O291" t="n">
-        <v>2</v>
-      </c>
-      <c r="P291" t="n">
-        <v>2</v>
-      </c>
-      <c r="U291" t="inlineStr">
-        <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V291" t="inlineStr">
-        <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W291" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X291" t="inlineStr">
-        <is>
-          <t>Salmonella Paratyphi infection</t>
-        </is>
-      </c>
-      <c r="Y291" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z291" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA291" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB291" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC291" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD291" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE291" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF291" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG291" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH291" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI291" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ291" t="inlineStr">
-        <is>
-          <t>US_NNDSS_Paratyphi_current</t>
-        </is>
-      </c>
-      <c r="AK291" t="inlineStr">
-        <is>
-          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
-        </is>
-      </c>
-      <c r="AM291" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN291" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO291" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP291" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ291" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS291" t="inlineStr">
-        <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT291" t="n">
-        <v>1</v>
-      </c>
       <c r="AU291" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV291" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW291" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX291" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY291" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ291" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA291" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB291" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC291" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -56773,12 +56767,12 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
@@ -56803,7 +56797,7 @@
       </c>
       <c r="L292" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M292" t="inlineStr">
@@ -56812,16 +56806,16 @@
         </is>
       </c>
       <c r="N292" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O292" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P292" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R292" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S292" t="inlineStr">
         <is>
@@ -56830,7 +56824,7 @@
       </c>
       <c r="U292" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AA292" t="inlineStr">
@@ -56840,7 +56834,7 @@
       </c>
       <c r="AO292" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP292" t="inlineStr">
@@ -56850,12 +56844,12 @@
       </c>
       <c r="AQ292" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS292" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT292" t="n">
@@ -56863,47 +56857,47 @@
       </c>
       <c r="AU292" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV292" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW292" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX292" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY292" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ292" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA292" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB292" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC292" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -56935,12 +56929,12 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -56965,7 +56959,7 @@
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -56974,32 +56968,32 @@
         </is>
       </c>
       <c r="N293" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O293" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P293" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U293" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="V293" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="W293" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X293" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Salmonella Paratyphi infection</t>
         </is>
       </c>
       <c r="Y293" t="inlineStr">
@@ -57024,7 +57018,7 @@
       </c>
       <c r="AC293" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD293" t="inlineStr">
@@ -57059,12 +57053,12 @@
       </c>
       <c r="AJ293" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>US_NNDSS_Paratyphi_current</t>
         </is>
       </c>
       <c r="AK293" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
         </is>
       </c>
       <c r="AM293" t="inlineStr">
@@ -57077,7 +57071,7 @@
       </c>
       <c r="AO293" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP293" t="inlineStr">
@@ -57087,12 +57081,12 @@
       </c>
       <c r="AQ293" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS293" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT293" t="n">
@@ -57100,47 +57094,47 @@
       </c>
       <c r="AU293" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV293" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW293" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX293" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY293" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ293" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA293" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB293" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC293" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -57172,12 +57166,12 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -57227,6 +57221,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA294" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -57234,70 +57233,70 @@
       </c>
       <c r="AO294" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP294" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ294" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS294" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT294" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU294" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV294" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW294" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX294" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY294" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ294" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA294" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB294" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC294" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -57329,12 +57328,12 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
@@ -57378,22 +57377,22 @@
       </c>
       <c r="U295" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V295" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W295" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X295" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y295" t="inlineStr">
@@ -57403,7 +57402,7 @@
       </c>
       <c r="Z295" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA295" t="inlineStr">
@@ -57418,7 +57417,7 @@
       </c>
       <c r="AC295" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD295" t="inlineStr">
@@ -57453,17 +57452,17 @@
       </c>
       <c r="AJ295" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK295" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM295" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN295" t="b">
@@ -57471,70 +57470,70 @@
       </c>
       <c r="AO295" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP295" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ295" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS295" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT295" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU295" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV295" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW295" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX295" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY295" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ295" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA295" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB295" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC295" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -57566,12 +57565,12 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -57596,7 +57595,7 @@
       </c>
       <c r="L296" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M296" t="inlineStr">
@@ -57621,11 +57620,6 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U296" t="inlineStr">
-        <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA296" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -57633,70 +57627,70 @@
       </c>
       <c r="AO296" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP296" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ296" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS296" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT296" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU296" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV296" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW296" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX296" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY296" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ296" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA296" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB296" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC296" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -57728,12 +57722,12 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
@@ -57758,7 +57752,7 @@
       </c>
       <c r="L297" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M297" t="inlineStr">
@@ -57777,22 +57771,22 @@
       </c>
       <c r="U297" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="V297" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="W297" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X297" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y297" t="inlineStr">
@@ -57802,7 +57796,7 @@
       </c>
       <c r="Z297" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA297" t="inlineStr">
@@ -57817,7 +57811,7 @@
       </c>
       <c r="AC297" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD297" t="inlineStr">
@@ -57852,17 +57846,17 @@
       </c>
       <c r="AJ297" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK297" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM297" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN297" t="b">
@@ -57870,70 +57864,70 @@
       </c>
       <c r="AO297" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP297" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ297" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS297" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT297" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU297" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV297" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW297" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX297" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY297" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ297" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA297" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB297" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC297" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -57965,12 +57959,12 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
@@ -58020,6 +58014,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA298" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -58027,70 +58026,70 @@
       </c>
       <c r="AO298" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP298" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ298" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS298" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT298" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU298" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV298" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW298" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX298" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY298" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ298" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA298" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB298" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC298" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -58122,12 +58121,12 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
@@ -58171,22 +58170,22 @@
       </c>
       <c r="U299" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V299" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W299" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X299" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y299" t="inlineStr">
@@ -58196,7 +58195,7 @@
       </c>
       <c r="Z299" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA299" t="inlineStr">
@@ -58211,7 +58210,7 @@
       </c>
       <c r="AC299" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD299" t="inlineStr">
@@ -58246,17 +58245,17 @@
       </c>
       <c r="AJ299" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK299" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM299" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN299" t="b">
@@ -58264,70 +58263,70 @@
       </c>
       <c r="AO299" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP299" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ299" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS299" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT299" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU299" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV299" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW299" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX299" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY299" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ299" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA299" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB299" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC299" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -58359,12 +58358,12 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
@@ -58389,7 +58388,7 @@
       </c>
       <c r="L300" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M300" t="inlineStr">
@@ -58398,27 +58397,22 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O300" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P300" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R300" t="n">
-        <v>0.002450425222697299</v>
+        <v>0</v>
       </c>
       <c r="S300" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U300" t="inlineStr">
-        <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA300" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -58426,70 +58420,70 @@
       </c>
       <c r="AO300" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP300" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ300" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS300" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT300" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU300" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV300" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW300" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX300" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY300" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ300" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA300" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB300" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC300" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -58521,12 +58515,12 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -58551,7 +58545,7 @@
       </c>
       <c r="L301" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M301" t="inlineStr">
@@ -58560,32 +58554,32 @@
         </is>
       </c>
       <c r="N301" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O301" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P301" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U301" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="V301" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="W301" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X301" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y301" t="inlineStr">
@@ -58595,7 +58589,7 @@
       </c>
       <c r="Z301" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA301" t="inlineStr">
@@ -58610,7 +58604,7 @@
       </c>
       <c r="AC301" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD301" t="inlineStr">
@@ -58645,17 +58639,17 @@
       </c>
       <c r="AJ301" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK301" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM301" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN301" t="b">
@@ -58663,70 +58657,70 @@
       </c>
       <c r="AO301" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP301" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ301" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS301" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT301" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU301" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV301" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW301" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX301" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY301" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ301" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA301" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB301" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC301" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -58758,12 +58752,12 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
@@ -58797,22 +58791,27 @@
         </is>
       </c>
       <c r="N302" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O302" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P302" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R302" t="n">
-        <v>0</v>
+        <v>0.002450425222697299</v>
       </c>
       <c r="S302" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA302" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -58820,70 +58819,70 @@
       </c>
       <c r="AO302" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP302" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ302" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS302" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT302" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU302" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV302" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW302" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX302" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY302" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ302" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA302" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB302" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC302" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -58915,12 +58914,12 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -58954,32 +58953,32 @@
         </is>
       </c>
       <c r="N303" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O303" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P303" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U303" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V303" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W303" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X303" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y303" t="inlineStr">
@@ -58989,7 +58988,7 @@
       </c>
       <c r="Z303" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA303" t="inlineStr">
@@ -59004,7 +59003,7 @@
       </c>
       <c r="AC303" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD303" t="inlineStr">
@@ -59039,17 +59038,17 @@
       </c>
       <c r="AJ303" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK303" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM303" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN303" t="b">
@@ -59057,70 +59056,70 @@
       </c>
       <c r="AO303" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP303" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ303" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS303" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT303" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU303" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV303" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW303" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX303" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY303" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ303" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA303" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB303" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC303" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -59152,12 +59151,12 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
@@ -59182,12 +59181,12 @@
       </c>
       <c r="L304" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N304" t="n">
@@ -59196,6 +59195,9 @@
       <c r="O304" t="n">
         <v>0</v>
       </c>
+      <c r="P304" t="n">
+        <v>0</v>
+      </c>
       <c r="R304" t="n">
         <v>0</v>
       </c>
@@ -59204,82 +59206,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U304" t="inlineStr">
-        <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
-        </is>
-      </c>
       <c r="AA304" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO304" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP304" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ304" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS304" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT304" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU304" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV304" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW304" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX304" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY304" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ304" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA304" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB304" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC304" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -59311,12 +59308,12 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -59341,12 +59338,12 @@
       </c>
       <c r="L305" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N305" t="n">
@@ -59355,19 +59352,22 @@
       <c r="O305" t="n">
         <v>0</v>
       </c>
+      <c r="P305" t="n">
+        <v>0</v>
+      </c>
       <c r="U305" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="V305" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="W305" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X305" t="inlineStr">
@@ -59382,12 +59382,12 @@
       </c>
       <c r="Z305" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA305" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB305" t="inlineStr">
@@ -59397,7 +59397,7 @@
       </c>
       <c r="AC305" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD305" t="inlineStr">
@@ -59432,17 +59432,17 @@
       </c>
       <c r="AJ305" t="inlineStr">
         <is>
-          <t>AU_NINDSS_current</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK305" t="inlineStr">
         <is>
-          <t>Australia NINDSS paratyphoid-only notifications; excludes typhoid fever.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM305" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN305" t="b">
@@ -59450,70 +59450,70 @@
       </c>
       <c r="AO305" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP305" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ305" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS305" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT305" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU305" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV305" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW305" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX305" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY305" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ305" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA305" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB305" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC305" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -59545,12 +59545,12 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -59599,7 +59599,7 @@
       </c>
       <c r="U306" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA306" t="inlineStr">
@@ -59609,7 +59609,7 @@
       </c>
       <c r="AO306" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP306" t="inlineStr">
@@ -59619,12 +59619,12 @@
       </c>
       <c r="AQ306" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS306" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT306" t="n">
@@ -59632,47 +59632,47 @@
       </c>
       <c r="AU306" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV306" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW306" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX306" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY306" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ306" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA306" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB306" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC306" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -59704,12 +59704,12 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -59750,22 +59750,22 @@
       </c>
       <c r="U307" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V307" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W307" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_AU_NINDSS</t>
         </is>
       </c>
       <c r="X307" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y307" t="inlineStr">
@@ -59775,7 +59775,7 @@
       </c>
       <c r="Z307" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA307" t="inlineStr">
@@ -59790,7 +59790,7 @@
       </c>
       <c r="AC307" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:AU:national</t>
         </is>
       </c>
       <c r="AD307" t="inlineStr">
@@ -59825,17 +59825,17 @@
       </c>
       <c r="AJ307" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>AU_NINDSS_current</t>
         </is>
       </c>
       <c r="AK307" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
+          <t>Australia NINDSS paratyphoid-only notifications; excludes typhoid fever.</t>
         </is>
       </c>
       <c r="AM307" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN307" t="b">
@@ -59843,7 +59843,7 @@
       </c>
       <c r="AO307" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP307" t="inlineStr">
@@ -59853,12 +59853,12 @@
       </c>
       <c r="AQ307" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS307" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT307" t="n">
@@ -59866,47 +59866,47 @@
       </c>
       <c r="AU307" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV307" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW307" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX307" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY307" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ307" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA307" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB307" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC307" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -59938,12 +59938,12 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -59977,13 +59977,13 @@
         </is>
       </c>
       <c r="N308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O308" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R308" t="n">
-        <v>0</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S308" t="inlineStr">
         <is>
@@ -59992,7 +59992,7 @@
       </c>
       <c r="U308" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AA308" t="inlineStr">
@@ -60012,12 +60012,12 @@
       </c>
       <c r="AQ308" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS308" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AT308" t="n">
@@ -60025,47 +60025,47 @@
       </c>
       <c r="AU308" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV308" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW308" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX308" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY308" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ308" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA308" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB308" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC308" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -60097,12 +60097,12 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G309" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H309" t="inlineStr">
@@ -60136,29 +60136,29 @@
         </is>
       </c>
       <c r="N309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U309" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="V309" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="W309" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X309" t="inlineStr">
         <is>
-          <t>파라티푸스</t>
+          <t>Salmonella Paratyphi</t>
         </is>
       </c>
       <c r="Y309" t="inlineStr">
@@ -60168,7 +60168,7 @@
       </c>
       <c r="Z309" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA309" t="inlineStr">
@@ -60183,7 +60183,7 @@
       </c>
       <c r="AC309" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD309" t="inlineStr">
@@ -60218,12 +60218,12 @@
       </c>
       <c r="AJ309" t="inlineStr">
         <is>
-          <t>KR_KDCA_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK309" t="inlineStr">
         <is>
-          <t>Korea KDCA paratyphoid-only notifications.</t>
+          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
         </is>
       </c>
       <c r="AM309" t="inlineStr">
@@ -60246,12 +60246,12 @@
       </c>
       <c r="AQ309" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS309" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AT309" t="n">
@@ -60259,47 +60259,47 @@
       </c>
       <c r="AU309" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV309" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW309" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX309" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY309" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ309" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA309" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB309" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC309" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -60331,12 +60331,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -60370,13 +60370,13 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R310" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S310" t="inlineStr">
         <is>
@@ -60385,7 +60385,7 @@
       </c>
       <c r="U310" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA310" t="inlineStr">
@@ -60410,7 +60410,7 @@
       </c>
       <c r="AS310" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT310" t="n">
@@ -60423,42 +60423,42 @@
       </c>
       <c r="AV310" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ310" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA310" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB310" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC310" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -60490,12 +60490,12 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -60529,29 +60529,29 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U311" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V311" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W311" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_KR_KDCA</t>
         </is>
       </c>
       <c r="X311" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>파라티푸스</t>
         </is>
       </c>
       <c r="Y311" t="inlineStr">
@@ -60561,7 +60561,7 @@
       </c>
       <c r="Z311" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -60576,7 +60576,7 @@
       </c>
       <c r="AC311" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:KR:national</t>
         </is>
       </c>
       <c r="AD311" t="inlineStr">
@@ -60611,17 +60611,17 @@
       </c>
       <c r="AJ311" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>KR_KDCA_current</t>
         </is>
       </c>
       <c r="AK311" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+          <t>Korea KDCA paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM311" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN311" t="b">
@@ -60644,7 +60644,7 @@
       </c>
       <c r="AS311" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT311" t="n">
@@ -60657,42 +60657,42 @@
       </c>
       <c r="AV311" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ311" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA311" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB311" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC311" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -60724,12 +60724,12 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -60754,7 +60754,7 @@
       </c>
       <c r="L312" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M312" t="inlineStr">
@@ -60768,11 +60768,8 @@
       <c r="O312" t="n">
         <v>1</v>
       </c>
-      <c r="P312" t="n">
-        <v>1</v>
-      </c>
       <c r="R312" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S312" t="inlineStr">
         <is>
@@ -60781,12 +60778,12 @@
       </c>
       <c r="U312" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO312" t="inlineStr">
@@ -60806,7 +60803,7 @@
       </c>
       <c r="AS312" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AT312" t="n">
@@ -60819,42 +60816,42 @@
       </c>
       <c r="AV312" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ312" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA312" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB312" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC312" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -60886,12 +60883,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -60916,7 +60913,7 @@
       </c>
       <c r="L313" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M313" t="inlineStr">
@@ -60930,27 +60927,24 @@
       <c r="O313" t="n">
         <v>1</v>
       </c>
-      <c r="P313" t="n">
-        <v>1</v>
-      </c>
       <c r="U313" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="V313" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="W313" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X313" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi infection</t>
+          <t>Paratyfoidfeber</t>
         </is>
       </c>
       <c r="Y313" t="inlineStr">
@@ -60960,12 +60954,12 @@
       </c>
       <c r="Z313" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA313" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB313" t="inlineStr">
@@ -60975,7 +60969,7 @@
       </c>
       <c r="AC313" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD313" t="inlineStr">
@@ -61010,17 +61004,17 @@
       </c>
       <c r="AJ313" t="inlineStr">
         <is>
-          <t>US_NNDSS_Paratyphi_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK313" t="inlineStr">
         <is>
-          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
         </is>
       </c>
       <c r="AM313" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN313" t="b">
@@ -61043,7 +61037,7 @@
       </c>
       <c r="AS313" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AT313" t="n">
@@ -61056,42 +61050,42 @@
       </c>
       <c r="AV313" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW313" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX313" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY313" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ313" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA313" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB313" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC313" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -61123,12 +61117,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -61153,7 +61147,7 @@
       </c>
       <c r="L314" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M314" t="inlineStr">
@@ -61162,16 +61156,16 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P314" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R314" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S314" t="inlineStr">
         <is>
@@ -61180,7 +61174,7 @@
       </c>
       <c r="U314" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AA314" t="inlineStr">
@@ -61190,7 +61184,7 @@
       </c>
       <c r="AO314" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP314" t="inlineStr">
@@ -61200,12 +61194,12 @@
       </c>
       <c r="AQ314" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS314" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT314" t="n">
@@ -61213,47 +61207,47 @@
       </c>
       <c r="AU314" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV314" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW314" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX314" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY314" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ314" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA314" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB314" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC314" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -61285,12 +61279,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -61315,7 +61309,7 @@
       </c>
       <c r="L315" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="M315" t="inlineStr">
@@ -61324,32 +61318,32 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U315" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="V315" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="W315" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X315" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Salmonella Paratyphi infection</t>
         </is>
       </c>
       <c r="Y315" t="inlineStr">
@@ -61374,7 +61368,7 @@
       </c>
       <c r="AC315" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD315" t="inlineStr">
@@ -61409,12 +61403,12 @@
       </c>
       <c r="AJ315" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>US_NNDSS_Paratyphi_current</t>
         </is>
       </c>
       <c r="AK315" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
         </is>
       </c>
       <c r="AM315" t="inlineStr">
@@ -61427,7 +61421,7 @@
       </c>
       <c r="AO315" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP315" t="inlineStr">
@@ -61437,12 +61431,12 @@
       </c>
       <c r="AQ315" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS315" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT315" t="n">
@@ -61450,47 +61444,47 @@
       </c>
       <c r="AU315" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV315" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW315" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX315" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY315" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ315" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA315" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB315" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC315" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -61522,12 +61516,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -61577,6 +61571,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA316" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -61584,70 +61583,70 @@
       </c>
       <c r="AO316" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP316" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ316" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS316" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT316" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU316" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV316" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW316" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX316" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY316" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ316" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA316" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB316" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC316" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -61679,12 +61678,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -61728,22 +61727,22 @@
       </c>
       <c r="U317" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V317" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W317" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X317" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y317" t="inlineStr">
@@ -61753,7 +61752,7 @@
       </c>
       <c r="Z317" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA317" t="inlineStr">
@@ -61768,7 +61767,7 @@
       </c>
       <c r="AC317" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD317" t="inlineStr">
@@ -61803,17 +61802,17 @@
       </c>
       <c r="AJ317" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK317" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM317" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN317" t="b">
@@ -61821,70 +61820,70 @@
       </c>
       <c r="AO317" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP317" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ317" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS317" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT317" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU317" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV317" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW317" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX317" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY317" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ317" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA317" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB317" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC317" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -61916,12 +61915,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -61946,7 +61945,7 @@
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -61955,27 +61954,22 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R318" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S318" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U318" t="inlineStr">
-        <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA318" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -61988,7 +61982,7 @@
       </c>
       <c r="AP318" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ318" t="inlineStr">
@@ -61998,55 +61992,55 @@
       </c>
       <c r="AS318" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT318" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU318" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV318" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW318" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX318" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY318" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ318" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA318" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB318" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC318" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -62078,212 +62072,1404 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N319" t="n">
+        <v>0</v>
+      </c>
+      <c r="O319" t="n">
+        <v>0</v>
+      </c>
+      <c r="P319" t="n">
+        <v>0</v>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="W319" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X319" t="inlineStr">
+        <is>
+          <t>Paratyphoid</t>
+        </is>
+      </c>
+      <c r="Y319" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA319" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB319" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC319" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD319" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE319" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF319" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG319" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH319" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI319" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ319" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK319" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM319" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN319" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO319" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP319" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ319" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS319" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT319" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU319" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV319" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW319" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX319" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY319" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ319" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA319" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB319" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC319" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G319" t="inlineStr">
+      <c r="G320" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H319" t="inlineStr">
-        <is>
-          <t>D234</t>
-        </is>
-      </c>
-      <c r="I319" t="inlineStr">
-        <is>
-          <t>Paratyphoid fever</t>
-        </is>
-      </c>
-      <c r="J319" t="inlineStr">
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
         <is>
           <t>副伤寒</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr">
+      <c r="K320" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L319" t="inlineStr">
+      <c r="L320" t="inlineStr">
         <is>
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="M319" t="inlineStr">
+      <c r="M320" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N319" t="n">
-        <v>1</v>
-      </c>
-      <c r="O319" t="n">
-        <v>1</v>
-      </c>
-      <c r="P319" t="n">
-        <v>1</v>
-      </c>
-      <c r="U319" t="inlineStr">
+      <c r="N320" t="n">
+        <v>1</v>
+      </c>
+      <c r="O320" t="n">
+        <v>1</v>
+      </c>
+      <c r="P320" t="n">
+        <v>1</v>
+      </c>
+      <c r="R320" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
         <is>
           <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
-      <c r="V319" t="inlineStr">
+      <c r="AA320" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO320" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP320" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ320" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS320" t="inlineStr">
         <is>
           <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
-      <c r="W319" t="inlineStr">
+      <c r="AT320" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU320" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV320" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW320" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX320" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY320" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ320" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA320" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB320" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC320" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N321" t="n">
+        <v>1</v>
+      </c>
+      <c r="O321" t="n">
+        <v>1</v>
+      </c>
+      <c r="P321" t="n">
+        <v>1</v>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W321" t="inlineStr">
         <is>
           <t>SRC_US_NNDSS</t>
         </is>
       </c>
-      <c r="X319" t="inlineStr">
+      <c r="X321" t="inlineStr">
         <is>
           <t>Salmonella Paratyphi infection</t>
         </is>
       </c>
-      <c r="Y319" t="inlineStr">
+      <c r="Y321" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z319" t="inlineStr">
+      <c r="Z321" t="inlineStr">
         <is>
           <t>notification</t>
         </is>
       </c>
-      <c r="AA319" t="inlineStr">
+      <c r="AA321" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB319" t="inlineStr">
+      <c r="AB321" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC319" t="inlineStr">
+      <c r="AC321" t="inlineStr">
         <is>
           <t>country:US:national</t>
         </is>
       </c>
-      <c r="AD319" t="inlineStr">
+      <c r="AD321" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE319" t="inlineStr">
+      <c r="AE321" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF319" t="inlineStr">
+      <c r="AF321" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG319" t="inlineStr">
+      <c r="AG321" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH319" t="inlineStr">
+      <c r="AH321" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI319" t="inlineStr">
+      <c r="AI321" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ319" t="inlineStr">
+      <c r="AJ321" t="inlineStr">
         <is>
           <t>US_NNDSS_Paratyphi_current</t>
         </is>
       </c>
-      <c r="AK319" t="inlineStr">
+      <c r="AK321" t="inlineStr">
         <is>
           <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
         </is>
       </c>
-      <c r="AM319" t="inlineStr">
+      <c r="AM321" t="inlineStr">
         <is>
           <t>provisional</t>
         </is>
       </c>
-      <c r="AN319" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO319" t="inlineStr">
+      <c r="AN321" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO321" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP319" t="inlineStr">
+      <c r="AP321" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ319" t="inlineStr">
+      <c r="AQ321" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS319" t="inlineStr">
+      <c r="AS321" t="inlineStr">
         <is>
           <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
-      <c r="AT319" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU319" t="inlineStr">
+      <c r="AT321" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU321" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV319" t="inlineStr">
+      <c r="AV321" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW319" t="inlineStr">
+      <c r="AW321" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX319" t="inlineStr">
+      <c r="AX321" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY319" t="inlineStr">
+      <c r="AY321" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ319" t="inlineStr">
+      <c r="AZ321" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA319" t="inlineStr">
+      <c r="BA321" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB319" t="inlineStr">
+      <c r="BB321" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC319" t="inlineStr">
+      <c r="BC321" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N322" t="n">
+        <v>1</v>
+      </c>
+      <c r="O322" t="n">
+        <v>1</v>
+      </c>
+      <c r="P322" t="n">
+        <v>1</v>
+      </c>
+      <c r="R322" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA322" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO322" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP322" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ322" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS322" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT322" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU322" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV322" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW322" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX322" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY322" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ322" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA322" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB322" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC322" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N323" t="n">
+        <v>1</v>
+      </c>
+      <c r="O323" t="n">
+        <v>1</v>
+      </c>
+      <c r="P323" t="n">
+        <v>1</v>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W323" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X323" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="Y323" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z323" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA323" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB323" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC323" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD323" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE323" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF323" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG323" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH323" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI323" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ323" t="inlineStr">
+        <is>
+          <t>JP_NIID_current</t>
+        </is>
+      </c>
+      <c r="AK323" t="inlineStr">
+        <is>
+          <t>Japan NIID paratyphoid-only notifications.</t>
+        </is>
+      </c>
+      <c r="AM323" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN323" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO323" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP323" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ323" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS323" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT323" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU323" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV323" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW323" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX323" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY323" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ323" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA323" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB323" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC323" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N324" t="n">
+        <v>0</v>
+      </c>
+      <c r="O324" t="n">
+        <v>0</v>
+      </c>
+      <c r="P324" t="n">
+        <v>0</v>
+      </c>
+      <c r="R324" t="n">
+        <v>0</v>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA324" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO324" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP324" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ324" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS324" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT324" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU324" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV324" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW324" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX324" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY324" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ324" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA324" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB324" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC324" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N325" t="n">
+        <v>0</v>
+      </c>
+      <c r="O325" t="n">
+        <v>0</v>
+      </c>
+      <c r="P325" t="n">
+        <v>0</v>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="W325" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X325" t="inlineStr">
+        <is>
+          <t>Paratyphoid</t>
+        </is>
+      </c>
+      <c r="Y325" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z325" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB325" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC325" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD325" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE325" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF325" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG325" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH325" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI325" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ325" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK325" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM325" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN325" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO325" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP325" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ325" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS325" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT325" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU325" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV325" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW325" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX325" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY325" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ325" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA325" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB325" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC325" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -62320,7 +63506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -62403,7 +63589,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10">
@@ -62413,7 +63599,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -62433,7 +63619,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13">
@@ -62465,7 +63651,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -63473,6 +63473,1984 @@
         </is>
       </c>
     </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N326" t="n">
+        <v>0</v>
+      </c>
+      <c r="O326" t="n">
+        <v>0</v>
+      </c>
+      <c r="P326" t="n">
+        <v>0</v>
+      </c>
+      <c r="R326" t="n">
+        <v>0</v>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA326" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO326" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP326" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ326" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS326" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT326" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU326" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV326" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW326" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX326" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY326" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ326" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA326" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB326" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC326" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N327" t="n">
+        <v>0</v>
+      </c>
+      <c r="O327" t="n">
+        <v>0</v>
+      </c>
+      <c r="P327" t="n">
+        <v>0</v>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W327" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X327" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="Y327" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA327" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB327" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC327" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD327" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE327" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF327" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG327" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH327" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI327" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ327" t="inlineStr">
+        <is>
+          <t>JP_NIID_current</t>
+        </is>
+      </c>
+      <c r="AK327" t="inlineStr">
+        <is>
+          <t>Japan NIID paratyphoid-only notifications.</t>
+        </is>
+      </c>
+      <c r="AM327" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN327" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO327" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP327" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ327" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS327" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT327" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU327" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV327" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW327" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX327" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY327" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ327" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA327" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB327" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC327" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N328" t="n">
+        <v>1</v>
+      </c>
+      <c r="O328" t="n">
+        <v>1</v>
+      </c>
+      <c r="P328" t="n">
+        <v>1</v>
+      </c>
+      <c r="R328" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA328" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO328" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP328" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ328" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS328" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT328" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU328" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV328" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW328" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX328" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY328" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ328" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA328" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB328" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC328" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N329" t="n">
+        <v>1</v>
+      </c>
+      <c r="O329" t="n">
+        <v>1</v>
+      </c>
+      <c r="P329" t="n">
+        <v>1</v>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="W329" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X329" t="inlineStr">
+        <is>
+          <t>Paratyphoid</t>
+        </is>
+      </c>
+      <c r="Y329" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z329" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA329" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB329" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC329" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD329" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE329" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF329" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG329" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI329" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ329" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK329" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM329" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN329" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO329" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP329" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ329" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS329" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT329" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU329" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV329" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW329" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX329" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY329" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ329" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA329" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB329" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC329" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N330" t="n">
+        <v>1</v>
+      </c>
+      <c r="O330" t="n">
+        <v>1</v>
+      </c>
+      <c r="P330" t="n">
+        <v>1</v>
+      </c>
+      <c r="R330" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO330" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP330" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ330" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS330" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT330" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU330" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV330" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW330" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX330" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY330" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ330" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA330" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB330" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC330" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N331" t="n">
+        <v>1</v>
+      </c>
+      <c r="O331" t="n">
+        <v>1</v>
+      </c>
+      <c r="P331" t="n">
+        <v>1</v>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W331" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>Salmonella Paratyphi infection</t>
+        </is>
+      </c>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z331" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB331" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC331" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD331" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE331" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF331" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG331" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH331" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI331" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ331" t="inlineStr">
+        <is>
+          <t>US_NNDSS_Paratyphi_current</t>
+        </is>
+      </c>
+      <c r="AK331" t="inlineStr">
+        <is>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
+        </is>
+      </c>
+      <c r="AM331" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN331" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO331" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP331" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ331" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS331" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT331" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU331" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV331" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW331" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX331" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY331" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ331" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA331" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB331" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC331" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N332" t="n">
+        <v>0</v>
+      </c>
+      <c r="O332" t="n">
+        <v>0</v>
+      </c>
+      <c r="R332" t="n">
+        <v>0</v>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1190</t>
+        </is>
+      </c>
+      <c r="AA332" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO332" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP332" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ332" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS332" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1190</t>
+        </is>
+      </c>
+      <c r="AT332" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU332" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV332" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW332" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX332" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY332" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ332" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA332" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB332" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC332" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M333" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N333" t="n">
+        <v>0</v>
+      </c>
+      <c r="O333" t="n">
+        <v>0</v>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1190</t>
+        </is>
+      </c>
+      <c r="V333" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1190</t>
+        </is>
+      </c>
+      <c r="W333" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X333" t="inlineStr">
+        <is>
+          <t>Salmonella Paratyphi</t>
+        </is>
+      </c>
+      <c r="Y333" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z333" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA333" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB333" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC333" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD333" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE333" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF333" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG333" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH333" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI333" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ333" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK333" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
+        </is>
+      </c>
+      <c r="AM333" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN333" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO333" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP333" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ333" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS333" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1190</t>
+        </is>
+      </c>
+      <c r="AT333" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU333" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+        </is>
+      </c>
+      <c r="AV333" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="AW333" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="AX333" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="AY333" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+      <c r="AZ333" t="inlineStr">
+        <is>
+          <t>thl_ttr</t>
+        </is>
+      </c>
+      <c r="BA333" t="inlineStr">
+        <is>
+          <t>Finland THL Infectious Diseases Register</t>
+        </is>
+      </c>
+      <c r="BB333" t="inlineStr">
+        <is>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+        </is>
+      </c>
+      <c r="BC333" t="inlineStr">
+        <is>
+          <t>cube_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M334" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N334" t="n">
+        <v>0</v>
+      </c>
+      <c r="O334" t="n">
+        <v>0</v>
+      </c>
+      <c r="R334" t="n">
+        <v>0</v>
+      </c>
+      <c r="S334" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO334" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP334" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ334" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS334" t="inlineStr">
+        <is>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT334" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU334" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV334" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW334" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX334" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY334" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ334" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA334" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB334" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC334" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M335" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N335" t="n">
+        <v>0</v>
+      </c>
+      <c r="O335" t="n">
+        <v>0</v>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V335" t="inlineStr">
+        <is>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W335" t="inlineStr">
+        <is>
+          <t>SRC_KR_KDCA</t>
+        </is>
+      </c>
+      <c r="X335" t="inlineStr">
+        <is>
+          <t>파라티푸스</t>
+        </is>
+      </c>
+      <c r="Y335" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z335" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA335" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB335" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC335" t="inlineStr">
+        <is>
+          <t>country:KR:national</t>
+        </is>
+      </c>
+      <c r="AD335" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE335" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF335" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG335" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH335" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI335" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ335" t="inlineStr">
+        <is>
+          <t>KR_KDCA_current</t>
+        </is>
+      </c>
+      <c r="AK335" t="inlineStr">
+        <is>
+          <t>Korea KDCA paratyphoid-only notifications.</t>
+        </is>
+      </c>
+      <c r="AM335" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN335" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO335" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP335" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ335" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS335" t="inlineStr">
+        <is>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT335" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU335" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV335" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW335" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX335" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY335" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ335" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA335" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB335" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC335" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -63506,7 +65484,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -63589,7 +65567,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10">
@@ -63599,7 +65577,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>324</v>
+        <v>334</v>
       </c>
     </row>
     <row r="11">
@@ -63619,7 +65597,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13">
@@ -63651,7 +65629,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -59584,13 +59584,13 @@
         </is>
       </c>
       <c r="N306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R306" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S306" t="inlineStr">
         <is>
@@ -59743,10 +59743,10 @@
         </is>
       </c>
       <c r="N307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U307" t="inlineStr">
         <is>
@@ -65629,7 +65629,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN11" t="b">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -14867,7 +14867,7 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN74" t="b">
@@ -22153,7 +22153,7 @@
       </c>
       <c r="AM111" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN111" t="b">
@@ -29441,7 +29441,7 @@
       </c>
       <c r="AM148" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN148" t="b">
@@ -38357,7 +38357,7 @@
       </c>
       <c r="AM195" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN195" t="b">
@@ -46719,7 +46719,7 @@
       </c>
       <c r="AM239" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN239" t="b">
@@ -53893,7 +53893,7 @@
       </c>
       <c r="AM277" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN277" t="b">
@@ -61014,7 +61014,7 @@
       </c>
       <c r="AM313" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN313" t="b">

--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -76738,13 +76738,13 @@
         </is>
       </c>
       <c r="N394" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O394" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R394" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.007345623639039581</v>
       </c>
       <c r="S394" t="inlineStr">
         <is>
@@ -76897,10 +76897,10 @@
         </is>
       </c>
       <c r="N395" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O395" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U395" t="inlineStr">
         <is>
@@ -86759,13 +86759,13 @@
         </is>
       </c>
       <c r="N445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R445" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S445" t="inlineStr">
         <is>
@@ -86918,10 +86918,10 @@
         </is>
       </c>
       <c r="N446" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O446" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U446" t="inlineStr">
         <is>
@@ -87481,6 +87481,405 @@
       <c r="BC448" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J449" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L449" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M449" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N449" t="n">
+        <v>0</v>
+      </c>
+      <c r="O449" t="n">
+        <v>0</v>
+      </c>
+      <c r="P449" t="n">
+        <v>0</v>
+      </c>
+      <c r="R449" t="n">
+        <v>0</v>
+      </c>
+      <c r="S449" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U449" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA449" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO449" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP449" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ449" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS449" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT449" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU449" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV449" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW449" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX449" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY449" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ449" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA449" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB449" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC449" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J450" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L450" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M450" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N450" t="n">
+        <v>0</v>
+      </c>
+      <c r="O450" t="n">
+        <v>0</v>
+      </c>
+      <c r="P450" t="n">
+        <v>0</v>
+      </c>
+      <c r="U450" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V450" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W450" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X450" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="Y450" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z450" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA450" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB450" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC450" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD450" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE450" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF450" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG450" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH450" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI450" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ450" t="inlineStr">
+        <is>
+          <t>JP_NIID_current</t>
+        </is>
+      </c>
+      <c r="AK450" t="inlineStr">
+        <is>
+          <t>Japan NIID paratyphoid-only notifications.</t>
+        </is>
+      </c>
+      <c r="AM450" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN450" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO450" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP450" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ450" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS450" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT450" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU450" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV450" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW450" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX450" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY450" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ450" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA450" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB450" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC450" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -87517,7 +87916,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -87600,7 +87999,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
@@ -87610,7 +88009,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>447</v>
+        <v>449</v>
       </c>
     </row>
     <row r="11">
@@ -87630,7 +88029,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="13">
@@ -87662,7 +88061,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16">
